--- a/examples/quickstart/Tables/06_differentiation.xlsx
+++ b/examples/quickstart/Tables/06_differentiation.xlsx
@@ -520,7 +520,7 @@
         <v>0.0002135847660514549</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3726047565502707</v>
+        <v>0.372604756550271</v>
       </c>
       <c r="I2" t="n">
         <v>0.06251395591871456</v>
@@ -529,10 +529,10 @@
         <v>0.01232926788817494</v>
       </c>
       <c r="K2" t="n">
-        <v>9.223315571845119e-06</v>
+        <v>9.223315571559103e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004202858508865282</v>
+        <v>0.004202858508864753</v>
       </c>
       <c r="M2" t="n">
         <v>0.0025044622044621</v>
@@ -570,10 +570,10 @@
         <v>0.0152481475522054</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002383059539019524</v>
+        <v>0.002383059539019626</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001434853370975427</v>
+        <v>0.001434853370975548</v>
       </c>
       <c r="M3" t="n">
         <v>0.0142682084582083</v>
@@ -602,7 +602,7 @@
         <v>0.0004024784672559177</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2984699040772086</v>
+        <v>0.2984699040772013</v>
       </c>
       <c r="I4" t="n">
         <v>0.2558400143572802</v>
@@ -611,10 +611,10 @@
         <v>0.01538406234577655</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0216792144804013</v>
+        <v>0.02167921448040865</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005618321029892937</v>
+        <v>0.005618321029907635</v>
       </c>
       <c r="M4" t="n">
         <v>0.3091520612720612</v>
@@ -643,7 +643,7 @@
         <v>0.0002024449168684714</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3726046076195335</v>
+        <v>0.3726046076195347</v>
       </c>
       <c r="I5" t="n">
         <v>0.06262242910897033</v>
@@ -652,10 +652,10 @@
         <v>0.01234040773735783</v>
       </c>
       <c r="K5" t="n">
-        <v>9.372246309104202e-06</v>
+        <v>9.372246307871074e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004322769409778509</v>
+        <v>0.004322769409776045</v>
       </c>
       <c r="M5" t="n">
         <v>0.0019912187812187</v>
@@ -684,7 +684,7 @@
         <v>0.0003994983150734293</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2998023761426925</v>
+        <v>0.2998023761426854</v>
       </c>
       <c r="I6" t="n">
         <v>0.2552494374308107</v>
@@ -693,10 +693,10 @@
         <v>0.01536263680120382</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02116547410181562</v>
+        <v>0.02116547410182273</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005541002736757987</v>
+        <v>0.005541002736772192</v>
       </c>
       <c r="M6" t="n">
         <v>0.3187867266067265</v>
@@ -725,7 +725,7 @@
         <v>3.388743807463408e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3227901197895205</v>
+        <v>0.3227901197895204</v>
       </c>
       <c r="I7" t="n">
         <v>0.2740888600549078</v>
@@ -734,10 +734,10 @@
         <v>0.01575311496431267</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01318141706029211</v>
+        <v>0.01318141706029219</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000686618268204677</v>
+        <v>0.0006866182682050102</v>
       </c>
       <c r="M7" t="n">
         <v>0.005862564102564</v>
@@ -766,7 +766,7 @@
         <v>0.0002010508423121267</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3726045821118505</v>
+        <v>0.3726045821118483</v>
       </c>
       <c r="I8" t="n">
         <v>0.06264115500746462</v>
@@ -775,10 +775,10 @@
         <v>0.01234180181191423</v>
       </c>
       <c r="K8" t="n">
-        <v>9.397753992110634e-06</v>
+        <v>9.397753994323555e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004342940398195074</v>
+        <v>0.004342940398199485</v>
       </c>
       <c r="M8" t="n">
         <v>0.001560829170829</v>
@@ -807,7 +807,7 @@
         <v>0.0002841721394376899</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2984613163008994</v>
+        <v>0.2984613163008992</v>
       </c>
       <c r="I9" t="n">
         <v>0.2615394113523647</v>
@@ -816,10 +816,10 @@
         <v>0.01561453733404254</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0240387725606991</v>
+        <v>0.02403877256069929</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004471851160880932</v>
+        <v>0.004471851160881206</v>
       </c>
       <c r="M9" t="n">
         <v>0.296870362970363</v>
@@ -848,7 +848,7 @@
         <v>0.0003980762614920594</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3001203247009366</v>
+        <v>0.3001203247009296</v>
       </c>
       <c r="I10" t="n">
         <v>0.2552632743501835</v>
@@ -857,10 +857,10 @@
         <v>0.01536321939602527</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02119205891585318</v>
+        <v>0.02119205891586024</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005519784831226935</v>
+        <v>0.005519784831241053</v>
       </c>
       <c r="M10" t="n">
         <v>0.3206637196137195</v>
@@ -889,7 +889,7 @@
         <v>9.317863586957269e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3659440152319511</v>
+        <v>0.3659440152319522</v>
       </c>
       <c r="I11" t="n">
         <v>0.1696711192950436</v>
@@ -898,10 +898,10 @@
         <v>0.01405521930036614</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0104353400589934</v>
+        <v>0.01043534005899224</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0024434439026245</v>
+        <v>0.002443443902622125</v>
       </c>
       <c r="M11" t="n">
         <v>0.0026510989010988</v>
@@ -930,7 +930,7 @@
         <v>0.0004105790910807878</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3004568656708626</v>
+        <v>0.3004568656708557</v>
       </c>
       <c r="I12" t="n">
         <v>0.2543867729048533</v>
@@ -939,10 +939,10 @@
         <v>0.01533575925308176</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02109393573052443</v>
+        <v>0.02109393573053146</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005520224189786599</v>
+        <v>0.005520224189800654</v>
       </c>
       <c r="M12" t="n">
         <v>0.3221609224109222</v>
@@ -971,7 +971,7 @@
         <v>0.0004270987518794283</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3008996236316719</v>
+        <v>0.3008996236316649</v>
       </c>
       <c r="I13" t="n">
         <v>0.2532341597854429</v>
@@ -980,10 +980,10 @@
         <v>0.01529956105229968</v>
       </c>
       <c r="K13" t="n">
-        <v>0.020964851341678</v>
+        <v>0.02096485134168497</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005521307105034961</v>
+        <v>0.005521307105048908</v>
       </c>
       <c r="M13" t="n">
         <v>0.3241521411921409</v>
@@ -1012,7 +1012,7 @@
         <v>3.914967069420108e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3037191832417623</v>
+        <v>0.3037191832417632</v>
       </c>
       <c r="I14" t="n">
         <v>0.2491617032006188</v>
@@ -1021,10 +1021,10 @@
         <v>0.01584504198119769</v>
       </c>
       <c r="K14" t="n">
-        <v>0.004045164499336557</v>
+        <v>0.004045164499335716</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001662887241144</v>
+        <v>0.001662887241142301</v>
       </c>
       <c r="M14" t="n">
         <v>0.0038172727272727</v>
@@ -1053,7 +1053,7 @@
         <v>1.753587316200447e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2596993365688282</v>
+        <v>0.259699336568828</v>
       </c>
       <c r="I15" t="n">
         <v>0.2967362563736499</v>
@@ -1062,10 +1062,10 @@
         <v>0.01672195702009635</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03104682084309391</v>
+        <v>0.03104682084309404</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0005348379639036544</v>
+        <v>0.0005348379639039107</v>
       </c>
       <c r="M15" t="n">
         <v>0.0032413653013652</v>
@@ -1094,7 +1094,7 @@
         <v>0.0001999989791658345</v>
       </c>
       <c r="H16" t="n">
-        <v>0.372604570627053</v>
+        <v>0.3726045706270518</v>
       </c>
       <c r="I16" t="n">
         <v>0.06264988518807471</v>
@@ -1103,10 +1103,10 @@
         <v>0.01234285367506057</v>
       </c>
       <c r="K16" t="n">
-        <v>9.409238789656667e-06</v>
+        <v>9.409238790746258e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004352745411546712</v>
+        <v>0.004352745411548888</v>
       </c>
       <c r="M16" t="n">
         <v>0.0016175124875124</v>
@@ -1135,7 +1135,7 @@
         <v>0.0004399915160882513</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3012428862541011</v>
+        <v>0.3012428862540941</v>
       </c>
       <c r="I17" t="n">
         <v>0.2523408593614939</v>
@@ -1144,10 +1144,10 @@
         <v>0.01527141136090002</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02086478231253144</v>
+        <v>0.02086478231253841</v>
       </c>
       <c r="L17" t="n">
-        <v>0.005522413601715455</v>
+        <v>0.0055224136017294</v>
       </c>
       <c r="M17" t="n">
         <v>0.3257129703629699</v>
@@ -1176,7 +1176,7 @@
         <v>8.587626850997031e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3655891805507551</v>
+        <v>0.3655891805507541</v>
       </c>
       <c r="I18" t="n">
         <v>0.1752617569664675</v>
@@ -1185,10 +1185,10 @@
         <v>0.01414617942556234</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01098637155195587</v>
+        <v>0.01098637155195685</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002375502831774064</v>
+        <v>0.002375502831776077</v>
       </c>
       <c r="M18" t="n">
         <v>0.0016520712620712</v>
@@ -1226,10 +1226,10 @@
         <v>0.0156320479778667</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01439419579661045</v>
+        <v>0.01439419579661044</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0008982120838978441</v>
+        <v>0.000898212083897735</v>
       </c>
       <c r="M19" t="n">
         <v>0.0102196303696303</v>
@@ -1258,7 +1258,7 @@
         <v>0.0001283900118674791</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3742288013572247</v>
+        <v>0.3742288013572246</v>
       </c>
       <c r="I20" t="n">
         <v>0.1209347076923169</v>
@@ -1267,10 +1267,10 @@
         <v>0.01314048312196129</v>
       </c>
       <c r="K20" t="n">
-        <v>8.786463192310957e-05</v>
+        <v>8.786463192323829e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004130757614497819</v>
+        <v>0.004130757614498048</v>
       </c>
       <c r="M20" t="n">
         <v>0.0030287079587079</v>
@@ -1299,7 +1299,7 @@
         <v>0.0002047800362197104</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3726046310656788</v>
+        <v>0.3726046310656789</v>
       </c>
       <c r="I21" t="n">
         <v>0.062604693524274</v>
@@ -1308,10 +1308,10 @@
         <v>0.01233807261800669</v>
       </c>
       <c r="K21" t="n">
-        <v>9.34880016379526e-06</v>
+        <v>9.34880016366474e-06</v>
       </c>
       <c r="L21" t="n">
-        <v>0.00430265181344035</v>
+        <v>0.00430265181344009</v>
       </c>
       <c r="M21" t="n">
         <v>0.0017140459540459</v>
@@ -1340,7 +1340,7 @@
         <v>0.0004385106530198693</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3015294806554844</v>
+        <v>0.3015294806554775</v>
       </c>
       <c r="I22" t="n">
         <v>0.2523663221120631</v>
@@ -1349,10 +1349,10 @@
         <v>0.01527238631645311</v>
       </c>
       <c r="K22" t="n">
-        <v>0.020893260392867</v>
+        <v>0.02089326039287393</v>
       </c>
       <c r="L22" t="n">
-        <v>0.005503434402074805</v>
+        <v>0.00550343440208867</v>
       </c>
       <c r="M22" t="n">
         <v>0.3275006793206788</v>
@@ -1381,7 +1381,7 @@
         <v>5.466260579055284e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3231680428733098</v>
+        <v>0.3231680428733105</v>
       </c>
       <c r="I23" t="n">
         <v>0.202358954659162</v>
@@ -1390,10 +1390,10 @@
         <v>0.01451489526986119</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0002437707853216493</v>
+        <v>0.0002437707853209465</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003112789705382598</v>
+        <v>0.003112789705381193</v>
       </c>
       <c r="M23" t="n">
         <v>0.008684935064935</v>
@@ -1422,7 +1422,7 @@
         <v>0.0002138412318858406</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3726047976188777</v>
+        <v>0.3726047976188772</v>
       </c>
       <c r="I24" t="n">
         <v>0.06248605136654522</v>
@@ -1431,10 +1431,10 @@
         <v>0.01232901142234051</v>
       </c>
       <c r="K24" t="n">
-        <v>9.182246964901489e-06</v>
+        <v>9.182246965360469e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004174615353647613</v>
+        <v>0.004174615353648528</v>
       </c>
       <c r="M24" t="n">
         <v>0.0047785114885114</v>
@@ -1463,7 +1463,7 @@
         <v>0.0002099231036098636</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3726047054532191</v>
+        <v>0.3726047054532176</v>
       </c>
       <c r="I25" t="n">
         <v>0.06255058529108297</v>
@@ -1472,10 +1472,10 @@
         <v>0.01233292955061647</v>
       </c>
       <c r="K25" t="n">
-        <v>9.274412623470705e-06</v>
+        <v>9.274412625078329e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004243251737778357</v>
+        <v>0.004243251737781619</v>
       </c>
       <c r="M25" t="n">
         <v>0.0022678288378288</v>
@@ -1504,7 +1504,7 @@
         <v>0.000198431570282773</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3726045488470552</v>
+        <v>0.3726045488470555</v>
       </c>
       <c r="I26" t="n">
         <v>0.06266625763694161</v>
@@ -1513,10 +1513,10 @@
         <v>0.01234442108394363</v>
       </c>
       <c r="K26" t="n">
-        <v>9.431018787393245e-06</v>
+        <v>9.431018787009012e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>0.004370728829292108</v>
+        <v>0.004370728829291341</v>
       </c>
       <c r="M26" t="n">
         <v>0.0014710123210122</v>
@@ -1545,7 +1545,7 @@
         <v>0.0004452037128313509</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3017047990649813</v>
+        <v>0.3017047990649744</v>
       </c>
       <c r="I27" t="n">
         <v>0.2519083420529625</v>
@@ -1554,10 +1554,10 @@
         <v>0.01525787027646979</v>
       </c>
       <c r="K27" t="n">
-        <v>0.02084188124273589</v>
+        <v>0.0208418812427428</v>
       </c>
       <c r="L27" t="n">
-        <v>0.005504185736340477</v>
+        <v>0.005504185736354302</v>
       </c>
       <c r="M27" t="n">
         <v>0.3283113919413914</v>
@@ -1586,7 +1586,7 @@
         <v>0.0002989899457249022</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2988866793762129</v>
+        <v>0.2988866793762128</v>
       </c>
       <c r="I28" t="n">
         <v>0.2604166504517381</v>
@@ -1595,10 +1595,10 @@
         <v>0.01558045498268373</v>
       </c>
       <c r="K28" t="n">
-        <v>0.02390109199508777</v>
+        <v>0.02390109199508795</v>
       </c>
       <c r="L28" t="n">
-        <v>0.004475369153598366</v>
+        <v>0.004475369153598627</v>
       </c>
       <c r="M28" t="n">
         <v>0.2985844089244089</v>
@@ -1627,7 +1627,7 @@
         <v>7.720956260034152e-05</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2587963722690004</v>
+        <v>0.2587963722690006</v>
       </c>
       <c r="I29" t="n">
         <v>0.2161190961148232</v>
@@ -1636,10 +1636,10 @@
         <v>0.01547876766597854</v>
       </c>
       <c r="K29" t="n">
-        <v>0.02379644219179222</v>
+        <v>0.02379644219179208</v>
       </c>
       <c r="L29" t="n">
-        <v>0.002059322653917571</v>
+        <v>0.002059322653917358</v>
       </c>
       <c r="M29" t="n">
         <v>0.0020791341991341</v>
@@ -1668,7 +1668,7 @@
         <v>0.0001271782735913393</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3425763690349349</v>
+        <v>0.3425763690349346</v>
       </c>
       <c r="I30" t="n">
         <v>0.1300470170684768</v>
@@ -1677,10 +1677,10 @@
         <v>0.01341824633487934</v>
       </c>
       <c r="K30" t="n">
-        <v>8.441988363840807e-05</v>
+        <v>8.441988363867396e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>0.004274629656434051</v>
+        <v>0.004274629656434582</v>
       </c>
       <c r="M30" t="n">
         <v>0.0030581451881451</v>
@@ -1709,7 +1709,7 @@
         <v>0.0001990550617643216</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3726045601221127</v>
+        <v>0.3726045601221134</v>
       </c>
       <c r="I31" t="n">
         <v>0.06265788094715082</v>
@@ -1718,10 +1718,10 @@
         <v>0.01234379759246203</v>
       </c>
       <c r="K31" t="n">
-        <v>9.419743729898469e-06</v>
+        <v>9.419743729155597e-06</v>
       </c>
       <c r="L31" t="n">
-        <v>0.004361706097904729</v>
+        <v>0.004361706097903234</v>
       </c>
       <c r="M31" t="n">
         <v>0.0016483316683316</v>
@@ -1750,7 +1750,7 @@
         <v>0.0004414159884268638</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3014012385181034</v>
+        <v>0.3014012385180965</v>
       </c>
       <c r="I32" t="n">
         <v>0.2522655258821279</v>
@@ -1759,10 +1759,10 @@
         <v>0.01527110069959086</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02100093000643947</v>
+        <v>0.0210009300064463</v>
       </c>
       <c r="L32" t="n">
-        <v>0.005460719689783251</v>
+        <v>0.005460719689796912</v>
       </c>
       <c r="M32" t="n">
         <v>0.332372064602064</v>
@@ -1791,7 +1791,7 @@
         <v>0.0002104017157631336</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3726047189355768</v>
+        <v>0.3726047189355772</v>
       </c>
       <c r="I33" t="n">
         <v>0.062541173773051</v>
@@ -1800,10 +1800,10 @@
         <v>0.01233245093846323</v>
       </c>
       <c r="K33" t="n">
-        <v>9.260930265717549e-06</v>
+        <v>9.260930265304768e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>0.00423333464287776</v>
+        <v>0.004233334642876934</v>
       </c>
       <c r="M33" t="n">
         <v>0.0027579154179153</v>
@@ -1832,7 +1832,7 @@
         <v>0.0004540980537748558</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3017290104157123</v>
+        <v>0.3017290104157055</v>
       </c>
       <c r="I34" t="n">
         <v>0.2514118486443822</v>
@@ -1841,10 +1841,10 @@
         <v>0.01524381061308425</v>
       </c>
       <c r="K34" t="n">
-        <v>0.02090456913367947</v>
+        <v>0.02090456913368626</v>
       </c>
       <c r="L34" t="n">
-        <v>0.00546278786013336</v>
+        <v>0.005462787860146955</v>
       </c>
       <c r="M34" t="n">
         <v>0.3339109590409584</v>
@@ -1873,7 +1873,7 @@
         <v>0.0001014314176145287</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3461363296215467</v>
+        <v>0.3461363296215464</v>
       </c>
       <c r="I35" t="n">
         <v>0.1584464768650159</v>
@@ -1882,10 +1882,10 @@
         <v>0.013872067058672</v>
       </c>
       <c r="K35" t="n">
-        <v>0.004198292251598191</v>
+        <v>0.004198292251598405</v>
       </c>
       <c r="L35" t="n">
-        <v>0.003527407264604529</v>
+        <v>0.003527407264604926</v>
       </c>
       <c r="M35" t="n">
         <v>0.0038538494838493</v>
@@ -1923,10 +1923,10 @@
         <v>0.01233328248502559</v>
       </c>
       <c r="K36" t="n">
-        <v>9.276518128762523e-06</v>
+        <v>9.276518128674978e-06</v>
       </c>
       <c r="L36" t="n">
-        <v>0.004244976031570482</v>
+        <v>0.004244976031570327</v>
       </c>
       <c r="M36" t="n">
         <v>0.0032881684981683</v>
@@ -1955,7 +1955,7 @@
         <v>0.0004598433311887781</v>
       </c>
       <c r="H37" t="n">
-        <v>0.301876822993248</v>
+        <v>0.3018768229932413</v>
       </c>
       <c r="I37" t="n">
         <v>0.2510270175347674</v>
@@ -1964,10 +1964,10 @@
         <v>0.01523147748684377</v>
       </c>
       <c r="K37" t="n">
-        <v>0.02086111708738548</v>
+        <v>0.02086111708739226</v>
       </c>
       <c r="L37" t="n">
-        <v>0.005463858894171711</v>
+        <v>0.005463858894185272</v>
       </c>
       <c r="M37" t="n">
         <v>0.334609633699633</v>
@@ -1996,7 +1996,7 @@
         <v>5.110170004523869e-05</v>
       </c>
       <c r="H38" t="n">
-        <v>0.370513956148559</v>
+        <v>0.3705139561485589</v>
       </c>
       <c r="I38" t="n">
         <v>0.1771316614456261</v>
@@ -2005,10 +2005,10 @@
         <v>0.01440171457531636</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0001384833413572483</v>
+        <v>0.0001384833413573807</v>
       </c>
       <c r="L38" t="n">
-        <v>0.004337548250701403</v>
+        <v>0.004337548250701748</v>
       </c>
       <c r="M38" t="n">
         <v>0.0063400765900765</v>
@@ -2037,7 +2037,7 @@
         <v>0.0002973809254346385</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2985094998422763</v>
+        <v>0.2985094998422762</v>
       </c>
       <c r="I39" t="n">
         <v>0.260658857396702</v>
@@ -2046,10 +2046,10 @@
         <v>0.01558903929746524</v>
       </c>
       <c r="K39" t="n">
-        <v>0.02398871531957751</v>
+        <v>0.02398871531957768</v>
       </c>
       <c r="L39" t="n">
-        <v>0.004452042151751925</v>
+        <v>0.004452042151752181</v>
       </c>
       <c r="M39" t="n">
         <v>0.3008627405927405</v>
@@ -2078,7 +2078,7 @@
         <v>0.0001978923652810975</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3726045496803796</v>
+        <v>0.3726045496803798</v>
       </c>
       <c r="I40" t="n">
         <v>0.06266491336443758</v>
@@ -2087,10 +2087,10 @@
         <v>0.0123449602889453</v>
       </c>
       <c r="K40" t="n">
-        <v>9.430185462950667e-06</v>
+        <v>9.430185462773039e-06</v>
       </c>
       <c r="L40" t="n">
-        <v>0.004369922095140858</v>
+        <v>0.004369922095140501</v>
       </c>
       <c r="M40" t="n">
         <v>0.0025830702630701</v>
@@ -2119,7 +2119,7 @@
         <v>0.0002097470367691784</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3726047022387399</v>
+        <v>0.3726047022387407</v>
       </c>
       <c r="I41" t="n">
         <v>0.06255220402805477</v>
@@ -2128,10 +2128,10 @@
         <v>0.0123331056174572</v>
       </c>
       <c r="K41" t="n">
-        <v>9.277627102573592e-06</v>
+        <v>9.277627101807302e-06</v>
       </c>
       <c r="L41" t="n">
-        <v>0.004245052970549211</v>
+        <v>0.004245052970547697</v>
       </c>
       <c r="M41" t="n">
         <v>0.0042316716616714</v>
@@ -2160,7 +2160,7 @@
         <v>0.001810436157889735</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3504642259565524</v>
+        <v>0.3504642259565515</v>
       </c>
       <c r="I42" t="n">
         <v>0.03409249165083172</v>
@@ -2169,10 +2169,10 @@
         <v>0.01223012117599836</v>
       </c>
       <c r="K42" t="n">
-        <v>4.710683291941398e-06</v>
+        <v>4.710683292755238e-06</v>
       </c>
       <c r="L42" t="n">
-        <v>0.01081047513233388</v>
+        <v>0.01081047513233546</v>
       </c>
       <c r="M42" t="n">
         <v>0.0010769597069596</v>
@@ -2201,7 +2201,7 @@
         <v>0.0001021619134560293</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3343810666207835</v>
+        <v>0.3343810666207839</v>
       </c>
       <c r="I43" t="n">
         <v>0.1705577057843724</v>
@@ -2210,10 +2210,10 @@
         <v>0.01400771253814704</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0001904460378017155</v>
+        <v>0.0001904460378013156</v>
       </c>
       <c r="L43" t="n">
-        <v>0.00326576318120937</v>
+        <v>0.003265763181208569</v>
       </c>
       <c r="M43" t="n">
         <v>0.0112326473526472</v>
@@ -2242,7 +2242,7 @@
         <v>0.0004567211907400004</v>
       </c>
       <c r="H44" t="n">
-        <v>0.301420698965193</v>
+        <v>0.3014206989651863</v>
       </c>
       <c r="I44" t="n">
         <v>0.2513782322248613</v>
@@ -2251,10 +2251,10 @@
         <v>0.01524450444465485</v>
       </c>
       <c r="K44" t="n">
-        <v>0.02101030979193458</v>
+        <v>0.02101030979194129</v>
       </c>
       <c r="L44" t="n">
-        <v>0.005430914646306619</v>
+        <v>0.005430914646320047</v>
       </c>
       <c r="M44" t="n">
         <v>0.3378509990009982</v>
@@ -2283,7 +2283,7 @@
         <v>0.0004639389782325184</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3016050390042218</v>
+        <v>0.301605039004215</v>
       </c>
       <c r="I45" t="n">
         <v>0.2509007496100293</v>
@@ -2292,10 +2292,10 @@
         <v>0.01522909724497573</v>
       </c>
       <c r="K45" t="n">
-        <v>0.02095609024140051</v>
+        <v>0.0209560902414072</v>
       </c>
       <c r="L45" t="n">
-        <v>0.00543257896182447</v>
+        <v>0.00543257896183785</v>
       </c>
       <c r="M45" t="n">
         <v>0.3387292973692965</v>
@@ -2324,7 +2324,7 @@
         <v>0.0001986183838510329</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3726045465571748</v>
+        <v>0.3726045465571765</v>
       </c>
       <c r="I46" t="n">
         <v>0.06266777193050237</v>
@@ -2333,10 +2333,10 @@
         <v>0.01234423427037531</v>
       </c>
       <c r="K46" t="n">
-        <v>9.433308667744675e-06</v>
+        <v>9.433308666139199e-06</v>
       </c>
       <c r="L46" t="n">
-        <v>0.00437206088904518</v>
+        <v>0.004372060889041973</v>
       </c>
       <c r="M46" t="n">
         <v>0.0012615684315683</v>
@@ -2365,7 +2365,7 @@
         <v>0.0002263767935347345</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3726049429117289</v>
+        <v>0.37260494291173</v>
       </c>
       <c r="I47" t="n">
         <v>0.06238504046564645</v>
@@ -2374,10 +2374,10 @@
         <v>0.01231647586069167</v>
       </c>
       <c r="K47" t="n">
-        <v>9.03695411375492e-06</v>
+        <v>9.036954112611327e-06</v>
       </c>
       <c r="L47" t="n">
-        <v>0.004060778305397669</v>
+        <v>0.004060778305395423</v>
       </c>
       <c r="M47" t="n">
         <v>0.0041647619047618</v>
@@ -2406,7 +2406,7 @@
         <v>0.0004695523762409267</v>
       </c>
       <c r="H48" t="n">
-        <v>0.301748020414675</v>
+        <v>0.3017480204146682</v>
       </c>
       <c r="I48" t="n">
         <v>0.2505304579334187</v>
@@ -2415,10 +2415,10 @@
         <v>0.01521713170726527</v>
       </c>
       <c r="K48" t="n">
-        <v>0.02091403713961985</v>
+        <v>0.02091403713962653</v>
       </c>
       <c r="L48" t="n">
-        <v>0.005433928873792869</v>
+        <v>0.005433928873806222</v>
       </c>
       <c r="M48" t="n">
         <v>0.339413702963702</v>
@@ -2447,7 +2447,7 @@
         <v>8.786559570870091e-05</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3094140807532667</v>
+        <v>0.309414080753268</v>
       </c>
       <c r="I49" t="n">
         <v>0.2006308560609383</v>
@@ -2456,10 +2456,10 @@
         <v>0.01470317722521758</v>
       </c>
       <c r="K49" t="n">
-        <v>0.008215772521440816</v>
+        <v>0.008215772521439553</v>
       </c>
       <c r="L49" t="n">
-        <v>0.001993136862586232</v>
+        <v>0.001993136862583697</v>
       </c>
       <c r="M49" t="n">
         <v>0.007284562104562</v>
@@ -2497,10 +2497,10 @@
         <v>0.01232451988803879</v>
       </c>
       <c r="K50" t="n">
-        <v>9.151643839258848e-06</v>
+        <v>9.151643839205241e-06</v>
       </c>
       <c r="L50" t="n">
-        <v>0.004147754332431309</v>
+        <v>0.004147754332431208</v>
       </c>
       <c r="M50" t="n">
         <v>0.003302604062604</v>
@@ -2529,7 +2529,7 @@
         <v>6.94862580181324e-05</v>
       </c>
       <c r="H51" t="n">
-        <v>0.322781988149785</v>
+        <v>0.3227819881497849</v>
       </c>
       <c r="I51" t="n">
         <v>0.1744194709954455</v>
@@ -2538,10 +2538,10 @@
         <v>0.01413740205297298</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0001166794542970151</v>
+        <v>0.0001166794542972126</v>
       </c>
       <c r="L51" t="n">
-        <v>0.004104341934492889</v>
+        <v>0.004104341934493201</v>
       </c>
       <c r="M51" t="n">
         <v>0.0049127705627705</v>
@@ -2570,7 +2570,7 @@
         <v>0.0004685897363669418</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3019273425086919</v>
+        <v>0.3019273425086852</v>
       </c>
       <c r="I52" t="n">
         <v>0.2505489098207372</v>
@@ -2579,10 +2579,10 @@
         <v>0.01521785653535085</v>
       </c>
       <c r="K52" t="n">
-        <v>0.02093475005434579</v>
+        <v>0.02093475005435244</v>
       </c>
       <c r="L52" t="n">
-        <v>0.005423035303649842</v>
+        <v>0.00542303530366315</v>
       </c>
       <c r="M52" t="n">
         <v>0.3406055577755568</v>
@@ -2611,7 +2611,7 @@
         <v>0.0003066685395407715</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2988935130460007</v>
+        <v>0.2988935130460006</v>
       </c>
       <c r="I53" t="n">
         <v>0.2593039999767051</v>
@@ -2620,10 +2620,10 @@
         <v>0.01555276732838288</v>
       </c>
       <c r="K53" t="n">
-        <v>0.02361113602209543</v>
+        <v>0.02361113602209563</v>
       </c>
       <c r="L53" t="n">
-        <v>0.004476148310230976</v>
+        <v>0.004476148310231268</v>
       </c>
       <c r="M53" t="n">
         <v>0.305775511155511</v>
@@ -2652,7 +2652,7 @@
         <v>0.000104428600680899</v>
       </c>
       <c r="H54" t="n">
-        <v>0.374183211591023</v>
+        <v>0.3741832115910228</v>
       </c>
       <c r="I54" t="n">
         <v>0.1182926937343337</v>
@@ -2661,10 +2661,10 @@
         <v>0.01312508326406268</v>
       </c>
       <c r="K54" t="n">
-        <v>4.114310863636474e-05</v>
+        <v>4.114310863662112e-05</v>
       </c>
       <c r="L54" t="n">
-        <v>0.004603603504668366</v>
+        <v>0.004603603504668879</v>
       </c>
       <c r="M54" t="n">
         <v>0.0031715984015983</v>
@@ -2693,7 +2693,7 @@
         <v>0.000226191950089361</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3726049457915409</v>
+        <v>0.3726049457915408</v>
       </c>
       <c r="I55" t="n">
         <v>0.06238386917057138</v>
@@ -2702,10 +2702,10 @@
         <v>0.01231666070413702</v>
       </c>
       <c r="K55" t="n">
-        <v>9.034074301643651e-06</v>
+        <v>9.03407430172344e-06</v>
       </c>
       <c r="L55" t="n">
-        <v>0.004059786094143711</v>
+        <v>0.004059786094143867</v>
       </c>
       <c r="M55" t="n">
         <v>0.0069636430236429</v>
@@ -2734,7 +2734,7 @@
         <v>0.0001905726617735755</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3423941483801941</v>
+        <v>0.3423941483801951</v>
       </c>
       <c r="I56" t="n">
         <v>0.1031606215382885</v>
@@ -2743,10 +2743,10 @@
         <v>0.01315214899642238</v>
       </c>
       <c r="K56" t="n">
-        <v>0.006322664895983037</v>
+        <v>0.006322664895982063</v>
       </c>
       <c r="L56" t="n">
-        <v>0.003488728894585876</v>
+        <v>0.003488728894583979</v>
       </c>
       <c r="M56" t="n">
         <v>0.004952437562437399</v>
@@ -2775,7 +2775,7 @@
         <v>0.0004614049044630658</v>
       </c>
       <c r="H57" t="n">
-        <v>0.3026442130767598</v>
+        <v>0.3026442130767532</v>
       </c>
       <c r="I57" t="n">
         <v>0.2507573787032809</v>
@@ -2784,10 +2784,10 @@
         <v>0.01522362894628101</v>
       </c>
       <c r="K57" t="n">
-        <v>0.02090393343878753</v>
+        <v>0.020903933438794</v>
       </c>
       <c r="L57" t="n">
-        <v>0.005341254573165786</v>
+        <v>0.005341254573178718</v>
       </c>
       <c r="M57" t="n">
         <v>0.3508251881451872</v>
@@ -2816,7 +2816,7 @@
         <v>0.0003061740945884061</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2986407746109526</v>
+        <v>0.2986407746109525</v>
       </c>
       <c r="I58" t="n">
         <v>0.2594179288281654</v>
@@ -2825,10 +2825,10 @@
         <v>0.01555688348709448</v>
       </c>
       <c r="K58" t="n">
-        <v>0.02365208978849352</v>
+        <v>0.02365208978849371</v>
       </c>
       <c r="L58" t="n">
-        <v>0.004469539136592388</v>
+        <v>0.004469539136592681</v>
       </c>
       <c r="M58" t="n">
         <v>0.3064235497835496</v>
@@ -2857,7 +2857,7 @@
         <v>0.0004576611872728902</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3028471914012593</v>
+        <v>0.3028471914012528</v>
       </c>
       <c r="I59" t="n">
         <v>0.2509217674990623</v>
@@ -2866,10 +2866,10 @@
         <v>0.01522854735090474</v>
       </c>
       <c r="K59" t="n">
-        <v>0.02090514749753312</v>
+        <v>0.02090514749753948</v>
       </c>
       <c r="L59" t="n">
-        <v>0.005298160367539593</v>
+        <v>0.005298160367552302</v>
       </c>
       <c r="M59" t="n">
         <v>0.3566877522477512</v>
@@ -2898,7 +2898,7 @@
         <v>0.0004711399772916556</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3031659797897692</v>
+        <v>0.3031659797897627</v>
       </c>
       <c r="I60" t="n">
         <v>0.2500835842970207</v>
@@ -2907,10 +2907,10 @@
         <v>0.01520067915139905</v>
       </c>
       <c r="K60" t="n">
-        <v>0.02081003411943722</v>
+        <v>0.02081003411944357</v>
       </c>
       <c r="L60" t="n">
-        <v>0.005303930373096958</v>
+        <v>0.005303930373109639</v>
       </c>
       <c r="M60" t="n">
         <v>0.3583280785880775</v>
@@ -2939,7 +2939,7 @@
         <v>0.0004711016000313051</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3031461254573133</v>
+        <v>0.3031461254573069</v>
       </c>
       <c r="I61" t="n">
         <v>0.2500599033523166</v>
@@ -2948,10 +2948,10 @@
         <v>0.01520295608795029</v>
       </c>
       <c r="K61" t="n">
-        <v>0.02065900581898784</v>
+        <v>0.02065900581899411</v>
       </c>
       <c r="L61" t="n">
-        <v>0.005298443381544446</v>
+        <v>0.005298443381556977</v>
       </c>
       <c r="M61" t="n">
         <v>0.3621453513153502</v>
@@ -2980,7 +2980,7 @@
         <v>0.0002062711458067809</v>
       </c>
       <c r="H62" t="n">
-        <v>0.372604658769152</v>
+        <v>0.3726046587691527</v>
       </c>
       <c r="I62" t="n">
         <v>0.06258468006065178</v>
@@ -2989,10 +2989,10 @@
         <v>0.01233658150841962</v>
       </c>
       <c r="K62" t="n">
-        <v>9.321096690572979e-06</v>
+        <v>9.321096689944345e-06</v>
       </c>
       <c r="L62" t="n">
-        <v>0.004281091833284525</v>
+        <v>0.004281091833283269</v>
       </c>
       <c r="M62" t="n">
         <v>0.0022345121545121</v>
@@ -3021,7 +3021,7 @@
         <v>0.0002131298771936168</v>
       </c>
       <c r="H63" t="n">
-        <v>0.3726047510294981</v>
+        <v>0.3726047510294966</v>
       </c>
       <c r="I63" t="n">
         <v>0.06251794049630829</v>
@@ -3030,10 +3030,10 @@
         <v>0.01232972277703268</v>
       </c>
       <c r="K63" t="n">
-        <v>9.228836344383748e-06</v>
+        <v>9.228836345935168e-06</v>
       </c>
       <c r="L63" t="n">
-        <v>0.004207309016861857</v>
+        <v>0.004207309016865004</v>
       </c>
       <c r="M63" t="n">
         <v>0.0025470263070262</v>
@@ -3062,7 +3062,7 @@
         <v>0.0001056674833888295</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2854407886396064</v>
+        <v>0.2854407886396065</v>
       </c>
       <c r="I64" t="n">
         <v>0.1801918701144603</v>
@@ -3071,10 +3071,10 @@
         <v>0.01474488640981574</v>
       </c>
       <c r="K64" t="n">
-        <v>0.01822750052769077</v>
+        <v>0.01822750052769066</v>
       </c>
       <c r="L64" t="n">
-        <v>0.002599056918383993</v>
+        <v>0.00259905691838383</v>
       </c>
       <c r="M64" t="n">
         <v>0.0027146886446885</v>
@@ -3103,7 +3103,7 @@
         <v>0.0004705110715853854</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3032715043922145</v>
+        <v>0.3032715043922081</v>
       </c>
       <c r="I65" t="n">
         <v>0.2500696181806409</v>
@@ -3112,10 +3112,10 @@
         <v>0.0152034038126124</v>
       </c>
       <c r="K65" t="n">
-        <v>0.02067820506498967</v>
+        <v>0.02067820506499593</v>
       </c>
       <c r="L65" t="n">
-        <v>0.005292057585831239</v>
+        <v>0.005292057585843736</v>
       </c>
       <c r="M65" t="n">
         <v>0.3630823643023631</v>
@@ -3144,7 +3144,7 @@
         <v>2.495193756903237e-06</v>
       </c>
       <c r="H66" t="n">
-        <v>0.3598251045604384</v>
+        <v>0.359825104560438</v>
       </c>
       <c r="I66" t="n">
         <v>0.2676031577758251</v>
@@ -3153,10 +3153,10 @@
         <v>0.01561622757765945</v>
       </c>
       <c r="K66" t="n">
-        <v>0.02000250289962416</v>
+        <v>0.02000250289962443</v>
       </c>
       <c r="L66" t="n">
-        <v>0.0006506589490538338</v>
+        <v>0.0006506589490543643</v>
       </c>
       <c r="M66" t="n">
         <v>0.0022874825174824</v>
@@ -3185,7 +3185,7 @@
         <v>0.0003057945538194356</v>
       </c>
       <c r="H67" t="n">
-        <v>0.2987661983385207</v>
+        <v>0.2987661983385206</v>
       </c>
       <c r="I67" t="n">
         <v>0.259416311329036</v>
@@ -3194,10 +3194,10 @@
         <v>0.01555671710116035</v>
       </c>
       <c r="K67" t="n">
-        <v>0.02365521815940994</v>
+        <v>0.02365521815941013</v>
       </c>
       <c r="L67" t="n">
-        <v>0.00446336697978845</v>
+        <v>0.004463366979788742</v>
       </c>
       <c r="M67" t="n">
         <v>0.3071097369297367</v>
@@ -3226,7 +3226,7 @@
         <v>0.0004915714926341798</v>
       </c>
       <c r="H68" t="n">
-        <v>0.3037603622018725</v>
+        <v>0.3037603622018662</v>
       </c>
       <c r="I68" t="n">
         <v>0.2487841209178341</v>
@@ -3235,10 +3235,10 @@
         <v>0.01516022548548459</v>
       </c>
       <c r="K68" t="n">
-        <v>0.02053311294353773</v>
+        <v>0.02053311294354393</v>
       </c>
       <c r="L68" t="n">
-        <v>0.005302717196385677</v>
+        <v>0.005302717196398053</v>
       </c>
       <c r="M68" t="n">
         <v>0.3656654345654332</v>
@@ -3267,7 +3267,7 @@
         <v>0.0004184161920148103</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3229789329253421</v>
+        <v>0.3229789329253407</v>
       </c>
       <c r="I69" t="n">
         <v>0.2417424648352855</v>
@@ -3276,10 +3276,10 @@
         <v>0.01485707249741633</v>
       </c>
       <c r="K69" t="n">
-        <v>0.002280668923135674</v>
+        <v>0.002280668923137094</v>
       </c>
       <c r="L69" t="n">
-        <v>0.001730523129956071</v>
+        <v>0.001730523129958834</v>
       </c>
       <c r="M69" t="n">
         <v>0.0149087845487843</v>
@@ -3308,7 +3308,7 @@
         <v>0.0002090071505490526</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3726046766063196</v>
+        <v>0.372604676606318</v>
       </c>
       <c r="I70" t="n">
         <v>0.0625723029037456</v>
@@ -3317,10 +3317,10 @@
         <v>0.01233384550367727</v>
       </c>
       <c r="K70" t="n">
-        <v>9.303259522992701e-06</v>
+        <v>9.303259524587048e-06</v>
       </c>
       <c r="L70" t="n">
-        <v>0.004265942997300946</v>
+        <v>0.004265942997304087</v>
       </c>
       <c r="M70" t="n">
         <v>0.0029783583083581</v>
@@ -3349,7 +3349,7 @@
         <v>0.0002103108761727119</v>
       </c>
       <c r="H71" t="n">
-        <v>0.3726047149477172</v>
+        <v>0.3726047149477183</v>
       </c>
       <c r="I71" t="n">
         <v>0.06254340253637693</v>
@@ -3358,10 +3358,10 @@
         <v>0.01233254177805369</v>
       </c>
       <c r="K71" t="n">
-        <v>9.264918125413253e-06</v>
+        <v>9.264918124313292e-06</v>
       </c>
       <c r="L71" t="n">
-        <v>0.004235662221513523</v>
+        <v>0.004235662221511352</v>
       </c>
       <c r="M71" t="n">
         <v>0.0036082384282383</v>
@@ -3390,7 +3390,7 @@
         <v>0.0004966449157811126</v>
       </c>
       <c r="H72" t="n">
-        <v>0.3038772164427424</v>
+        <v>0.3038772164427361</v>
       </c>
       <c r="I72" t="n">
         <v>0.2484769192193058</v>
@@ -3399,10 +3399,10 @@
         <v>0.01514986476195914</v>
       </c>
       <c r="K72" t="n">
-        <v>0.02049843612248702</v>
+        <v>0.0204984361224932</v>
       </c>
       <c r="L72" t="n">
-        <v>0.005305338855154368</v>
+        <v>0.005305338855166726</v>
       </c>
       <c r="M72" t="n">
         <v>0.3662883716283701</v>
@@ -3431,7 +3431,7 @@
         <v>0.0002014305388148949</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3726045827872734</v>
+        <v>0.3726045827872742</v>
       </c>
       <c r="I73" t="n">
         <v>0.06264043333054296</v>
@@ -3440,10 +3440,10 @@
         <v>0.01234142211541141</v>
       </c>
       <c r="K73" t="n">
-        <v>9.397078569119223e-06</v>
+        <v>9.397078568420479e-06</v>
       </c>
       <c r="L73" t="n">
-        <v>0.004341837673924658</v>
+        <v>0.00434183767392326</v>
       </c>
       <c r="M73" t="n">
         <v>0.0013576889776889</v>
@@ -3472,7 +3472,7 @@
         <v>0.0004981900631517083</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3041782958865995</v>
+        <v>0.3041782958865932</v>
       </c>
       <c r="I74" t="n">
         <v>0.2482168101113769</v>
@@ -3481,10 +3481,10 @@
         <v>0.01514196864441635</v>
       </c>
       <c r="K74" t="n">
-        <v>0.02043173687677128</v>
+        <v>0.02043173687677744</v>
       </c>
       <c r="L74" t="n">
-        <v>0.005309445723543703</v>
+        <v>0.005309445723556008</v>
       </c>
       <c r="M74" t="n">
         <v>0.3679404428904413</v>
@@ -3513,7 +3513,7 @@
         <v>0.0005119087518989167</v>
       </c>
       <c r="H75" t="n">
-        <v>0.3044909279742793</v>
+        <v>0.304490927974273</v>
       </c>
       <c r="I75" t="n">
         <v>0.2473926438075005</v>
@@ -3522,10 +3522,10 @@
         <v>0.01511407018566701</v>
       </c>
       <c r="K75" t="n">
-        <v>0.02033887155330037</v>
+        <v>0.0203388715533065</v>
       </c>
       <c r="L75" t="n">
-        <v>0.005316619423710329</v>
+        <v>0.00531661942372258</v>
       </c>
       <c r="M75" t="n">
         <v>0.3696326573426557</v>
@@ -3554,7 +3554,7 @@
         <v>0.0005213785923095499</v>
       </c>
       <c r="H76" t="n">
-        <v>0.3047057897490816</v>
+        <v>0.3047057897490753</v>
       </c>
       <c r="I76" t="n">
         <v>0.2468264221456827</v>
@@ -3563,10 +3563,10 @@
         <v>0.01509485460511966</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02027505523088175</v>
+        <v>0.02027505523088786</v>
       </c>
       <c r="L76" t="n">
-        <v>0.005321755642307719</v>
+        <v>0.005321755642319916</v>
       </c>
       <c r="M76" t="n">
         <v>0.3708047685647669</v>
@@ -3595,7 +3595,7 @@
         <v>0.0005172673688392396</v>
       </c>
       <c r="H77" t="n">
-        <v>0.3042286515018479</v>
+        <v>0.3042286515018418</v>
       </c>
       <c r="I77" t="n">
         <v>0.2471294611677558</v>
@@ -3604,10 +3604,10 @@
         <v>0.01510302160404756</v>
       </c>
       <c r="K77" t="n">
-        <v>0.02016890340136587</v>
+        <v>0.02016890340137186</v>
       </c>
       <c r="L77" t="n">
-        <v>0.005285824330384596</v>
+        <v>0.005285824330396549</v>
       </c>
       <c r="M77" t="n">
         <v>0.3783190875790859</v>
@@ -3636,7 +3636,7 @@
         <v>0.0005309179166828297</v>
       </c>
       <c r="H78" t="n">
-        <v>0.3045329010633189</v>
+        <v>0.3045329010633128</v>
       </c>
       <c r="I78" t="n">
         <v>0.2463329740826267</v>
@@ -3645,10 +3645,10 @@
         <v>0.01507564593515951</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02007969525762624</v>
+        <v>0.0200796952576322</v>
       </c>
       <c r="L78" t="n">
-        <v>0.005294277665271022</v>
+        <v>0.005294277665282922</v>
       </c>
       <c r="M78" t="n">
         <v>0.3800139194139177</v>
@@ -3677,7 +3677,7 @@
         <v>0.0005418032271245996</v>
       </c>
       <c r="H79" t="n">
-        <v>0.3047746645487036</v>
+        <v>0.3047746645486976</v>
       </c>
       <c r="I79" t="n">
         <v>0.2457004257488432</v>
@@ -3686,10 +3686,10 @@
         <v>0.01505385376423757</v>
       </c>
       <c r="K79" t="n">
-        <v>0.02000881745937376</v>
+        <v>0.02000881745937971</v>
       </c>
       <c r="L79" t="n">
-        <v>0.005301374262783985</v>
+        <v>0.005301374262795859</v>
       </c>
       <c r="M79" t="n">
         <v>0.3813716083916066</v>
@@ -3718,7 +3718,7 @@
         <v>0.0004129567109229497</v>
       </c>
       <c r="H80" t="n">
-        <v>0.326120717910197</v>
+        <v>0.3261207179101959</v>
       </c>
       <c r="I80" t="n">
         <v>0.2303569274997767</v>
@@ -3727,10 +3727,10 @@
         <v>0.01468953389862021</v>
       </c>
       <c r="K80" t="n">
-        <v>0.002136801101691062</v>
+        <v>0.002136801101692152</v>
       </c>
       <c r="L80" t="n">
-        <v>0.001840484929642977</v>
+        <v>0.001840484929645078</v>
       </c>
       <c r="M80" t="n">
         <v>0.0159164235764233</v>
@@ -3759,7 +3759,7 @@
         <v>0.001019509525825922</v>
       </c>
       <c r="H81" t="n">
-        <v>0.3641252581363003</v>
+        <v>0.3641252581362994</v>
       </c>
       <c r="I81" t="n">
         <v>0.05147897860475942</v>
@@ -3768,10 +3768,10 @@
         <v>0.01209694115735211</v>
       </c>
       <c r="K81" t="n">
-        <v>7.508231330841481e-06</v>
+        <v>7.50823133172626e-06</v>
       </c>
       <c r="L81" t="n">
-        <v>0.006389155752876869</v>
+        <v>0.006389155752878661</v>
       </c>
       <c r="M81" t="n">
         <v>0.004457096237096099</v>
@@ -3800,7 +3800,7 @@
         <v>0.0001771112997157457</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3428706156366212</v>
+        <v>0.3428706156366218</v>
       </c>
       <c r="I82" t="n">
         <v>0.1026587640633863</v>
@@ -3809,10 +3809,10 @@
         <v>0.01315299476455184</v>
       </c>
       <c r="K82" t="n">
-        <v>0.006223105543521569</v>
+        <v>0.006223105543520913</v>
       </c>
       <c r="L82" t="n">
-        <v>0.003653074738680638</v>
+        <v>0.003653074738679393</v>
       </c>
       <c r="M82" t="n">
         <v>0.005017036297036</v>
@@ -3850,10 +3850,10 @@
         <v>0.01384704105305358</v>
       </c>
       <c r="K83" t="n">
-        <v>0.0001737950391438516</v>
+        <v>0.0001737950391437236</v>
       </c>
       <c r="L83" t="n">
-        <v>0.003302793598210299</v>
+        <v>0.003302793598210034</v>
       </c>
       <c r="M83" t="n">
         <v>0.012364109224109</v>
@@ -3891,10 +3891,10 @@
         <v>0.01556565496905224</v>
       </c>
       <c r="K84" t="n">
-        <v>0.02374439977449676</v>
+        <v>0.02374439977449695</v>
       </c>
       <c r="L84" t="n">
-        <v>0.004449110673378394</v>
+        <v>0.004449110673378685</v>
       </c>
       <c r="M84" t="n">
         <v>0.3085303296703294</v>
@@ -3923,7 +3923,7 @@
         <v>0.0005402888564362733</v>
       </c>
       <c r="H85" t="n">
-        <v>0.3050481414111842</v>
+        <v>0.3050481414111783</v>
       </c>
       <c r="I85" t="n">
         <v>0.2457390124207851</v>
@@ -3932,10 +3932,10 @@
         <v>0.01505550565954053</v>
       </c>
       <c r="K85" t="n">
-        <v>0.02006352902679104</v>
+        <v>0.02006352902679696</v>
       </c>
       <c r="L85" t="n">
-        <v>0.005289439173815576</v>
+        <v>0.005289439173827382</v>
       </c>
       <c r="M85" t="n">
         <v>0.383659090909089</v>
@@ -3964,7 +3964,7 @@
         <v>0.0005458144030023814</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3051691061434252</v>
+        <v>0.3051691061434193</v>
       </c>
       <c r="I86" t="n">
         <v>0.2454213135653314</v>
@@ -3973,10 +3973,10 @@
         <v>0.01504449994786124</v>
       </c>
       <c r="K86" t="n">
-        <v>0.02002783303228248</v>
+        <v>0.02002783303228839</v>
       </c>
       <c r="L86" t="n">
-        <v>0.005293179645378862</v>
+        <v>0.005293179645390648</v>
       </c>
       <c r="M86" t="n">
         <v>0.3843490143190124</v>
@@ -4005,7 +4005,7 @@
         <v>0.0005631794234503448</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3055954263050071</v>
+        <v>0.3055954263050012</v>
       </c>
       <c r="I87" t="n">
         <v>0.2443854801568863</v>
@@ -4014,10 +4014,10 @@
         <v>0.01501536193644591</v>
       </c>
       <c r="K87" t="n">
-        <v>0.01988070629987175</v>
+        <v>0.0198807062998776</v>
       </c>
       <c r="L87" t="n">
-        <v>0.00532924997558332</v>
+        <v>0.005329249975595</v>
       </c>
       <c r="M87" t="n">
         <v>0.3872393140193121</v>
@@ -4046,7 +4046,7 @@
         <v>0.0005704133399444442</v>
       </c>
       <c r="H88" t="n">
-        <v>0.3057522190200451</v>
+        <v>0.3057522190200392</v>
       </c>
       <c r="I88" t="n">
         <v>0.2439737114810145</v>
@@ -4055,10 +4055,10 @@
         <v>0.01500100621861777</v>
       </c>
       <c r="K88" t="n">
-        <v>0.01983450014889083</v>
+        <v>0.01983450014889667</v>
       </c>
       <c r="L88" t="n">
-        <v>0.005334285496320135</v>
+        <v>0.005334285496331781</v>
       </c>
       <c r="M88" t="n">
         <v>0.3881499234099214</v>
@@ -4087,7 +4087,7 @@
         <v>0.0005810958870784206</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3067662047692238</v>
+        <v>0.3067662047692181</v>
       </c>
       <c r="I89" t="n">
         <v>0.2429292061983249</v>
@@ -4096,10 +4096,10 @@
         <v>0.01497234595217683</v>
       </c>
       <c r="K89" t="n">
-        <v>0.01954479161439938</v>
+        <v>0.01954479161440509</v>
       </c>
       <c r="L89" t="n">
-        <v>0.005382664604134928</v>
+        <v>0.005382664604146314</v>
       </c>
       <c r="M89" t="n">
         <v>0.3944899999999979</v>
@@ -4128,7 +4128,7 @@
         <v>0.0001504291803736037</v>
       </c>
       <c r="H90" t="n">
-        <v>0.3247943409484227</v>
+        <v>0.3247943409484229</v>
       </c>
       <c r="I90" t="n">
         <v>0.12710654768949</v>
@@ -4137,10 +4137,10 @@
         <v>0.01365822185281521</v>
       </c>
       <c r="K90" t="n">
-        <v>0.01000220308620885</v>
+        <v>0.01000220308620871</v>
       </c>
       <c r="L90" t="n">
-        <v>0.003372264141099188</v>
+        <v>0.003372264141098972</v>
       </c>
       <c r="M90" t="n">
         <v>0.004949200799200601</v>
@@ -4169,7 +4169,7 @@
         <v>0.002589181621747137</v>
       </c>
       <c r="H91" t="n">
-        <v>0.3473245546729553</v>
+        <v>0.3473245546729558</v>
       </c>
       <c r="I91" t="n">
         <v>0.02966518966639263</v>
@@ -4178,10 +4178,10 @@
         <v>0.01166375436666204</v>
       </c>
       <c r="K91" t="n">
-        <v>4.153757338977438e-06</v>
+        <v>4.153757338438651e-06</v>
       </c>
       <c r="L91" t="n">
-        <v>0.01079825185835542</v>
+        <v>0.0107982518583544</v>
       </c>
       <c r="M91" t="n">
         <v>0.0016576756576756</v>
@@ -4210,7 +4210,7 @@
         <v>0.00058892443569674</v>
       </c>
       <c r="H92" t="n">
-        <v>0.3069308545982564</v>
+        <v>0.3069308545982507</v>
       </c>
       <c r="I92" t="n">
         <v>0.2424932570156512</v>
@@ -4219,10 +4219,10 @@
         <v>0.01495696646958828</v>
       </c>
       <c r="K92" t="n">
-        <v>0.01949627545535988</v>
+        <v>0.01949627545536558</v>
       </c>
       <c r="L92" t="n">
-        <v>0.005388472981723974</v>
+        <v>0.005388472981735341</v>
       </c>
       <c r="M92" t="n">
         <v>0.3954819180819159</v>
@@ -4251,7 +4251,7 @@
         <v>0.0005880586824345497</v>
       </c>
       <c r="H93" t="n">
-        <v>0.3066489761979673</v>
+        <v>0.3066489761979616</v>
       </c>
       <c r="I93" t="n">
         <v>0.24263318079873</v>
@@ -4260,10 +4260,10 @@
         <v>0.01496218345143971</v>
       </c>
       <c r="K93" t="n">
-        <v>0.01955466245530597</v>
+        <v>0.01955466245531165</v>
       </c>
       <c r="L93" t="n">
-        <v>0.005383607822515178</v>
+        <v>0.005383607822526521</v>
       </c>
       <c r="M93" t="n">
         <v>0.3963330935730913</v>
@@ -4292,7 +4292,7 @@
         <v>0.0005997099022175092</v>
       </c>
       <c r="H94" t="n">
-        <v>0.3069414732704976</v>
+        <v>0.306941473270492</v>
       </c>
       <c r="I94" t="n">
         <v>0.2417277106722369</v>
@@ -4301,10 +4301,10 @@
         <v>0.01493336267288613</v>
       </c>
       <c r="K94" t="n">
-        <v>0.01938706572962294</v>
+        <v>0.0193870657296286</v>
       </c>
       <c r="L94" t="n">
-        <v>0.0054209305517597</v>
+        <v>0.005420930551770978</v>
       </c>
       <c r="M94" t="n">
         <v>0.3999056210456187</v>
@@ -4333,7 +4333,7 @@
         <v>0.0005987168717612695</v>
       </c>
       <c r="H95" t="n">
-        <v>0.3066203789550938</v>
+        <v>0.3066203789550881</v>
       </c>
       <c r="I95" t="n">
         <v>0.2418880452659856</v>
@@ -4342,10 +4342,10 @@
         <v>0.01493933573940883</v>
       </c>
       <c r="K95" t="n">
-        <v>0.0194542202554387</v>
+        <v>0.01945422025544434</v>
       </c>
       <c r="L95" t="n">
-        <v>0.005415593581840557</v>
+        <v>0.005415593581851807</v>
       </c>
       <c r="M95" t="n">
         <v>0.4008847952047928</v>
@@ -4374,7 +4374,7 @@
         <v>0.0006035073774799056</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3067087767692448</v>
+        <v>0.3067087767692394</v>
       </c>
       <c r="I96" t="n">
         <v>0.2413352197696928</v>
@@ -4383,10 +4383,10 @@
         <v>0.01492121341660912</v>
       </c>
       <c r="K96" t="n">
-        <v>0.01921510981397949</v>
+        <v>0.01921510981398502</v>
       </c>
       <c r="L96" t="n">
-        <v>0.005447015823077444</v>
+        <v>0.005447015823088468</v>
       </c>
       <c r="M96" t="n">
         <v>0.4081693573093548</v>
@@ -4415,7 +4415,7 @@
         <v>0.0006252842403164829</v>
       </c>
       <c r="H97" t="n">
-        <v>0.3071935347787175</v>
+        <v>0.3071935347787121</v>
       </c>
       <c r="I97" t="n">
         <v>0.2398454918362717</v>
@@ -4424,10 +4424,10 @@
         <v>0.01487278886660787</v>
       </c>
       <c r="K97" t="n">
-        <v>0.01901168706376947</v>
+        <v>0.01901168706377493</v>
       </c>
       <c r="L97" t="n">
-        <v>0.005501063519875883</v>
+        <v>0.00550106351988677</v>
       </c>
       <c r="M97" t="n">
         <v>0.4131863936063908</v>
@@ -4465,10 +4465,10 @@
         <v>0.01551541579145491</v>
       </c>
       <c r="K98" t="n">
-        <v>0.02354617002666783</v>
+        <v>0.02354617002666801</v>
       </c>
       <c r="L98" t="n">
-        <v>0.004456105435752672</v>
+        <v>0.004456105435752939</v>
       </c>
       <c r="M98" t="n">
         <v>0.3111350249750247</v>
@@ -4497,7 +4497,7 @@
         <v>0.0001311417456848229</v>
       </c>
       <c r="H99" t="n">
-        <v>0.3737809816370352</v>
+        <v>0.3737809816370358</v>
       </c>
       <c r="I99" t="n">
         <v>0.1040905779636877</v>
@@ -4506,10 +4506,10 @@
         <v>0.01292339924793884</v>
       </c>
       <c r="K99" t="n">
-        <v>3.302585809127478e-05</v>
+        <v>3.302585809079515e-05</v>
       </c>
       <c r="L99" t="n">
-        <v>0.00451374941596351</v>
+        <v>0.004513749415962579</v>
       </c>
       <c r="M99" t="n">
         <v>0.0042561205461204</v>
@@ -4538,7 +4538,7 @@
         <v>0.0003427774675212901</v>
       </c>
       <c r="H100" t="n">
-        <v>0.2992703805582361</v>
+        <v>0.299270380558236</v>
       </c>
       <c r="I100" t="n">
         <v>0.2569212985271502</v>
@@ -4547,10 +4547,10 @@
         <v>0.01548041813708433</v>
       </c>
       <c r="K100" t="n">
-        <v>0.02340863043180145</v>
+        <v>0.0234086304318016</v>
       </c>
       <c r="L100" t="n">
-        <v>0.004461463474771035</v>
+        <v>0.004461463474771239</v>
       </c>
       <c r="M100" t="n">
         <v>0.3129684681984679</v>
@@ -4579,7 +4579,7 @@
         <v>0.0006229397255765043</v>
       </c>
       <c r="H101" t="n">
-        <v>0.3070788008786036</v>
+        <v>0.3070788008785982</v>
       </c>
       <c r="I101" t="n">
         <v>0.2400612635471097</v>
@@ -4588,10 +4588,10 @@
         <v>0.0148809012659832</v>
       </c>
       <c r="K101" t="n">
-        <v>0.01914391987461964</v>
+        <v>0.01914391987462506</v>
       </c>
       <c r="L101" t="n">
-        <v>0.005490166701735593</v>
+        <v>0.005490166701746393</v>
       </c>
       <c r="M101" t="n">
         <v>0.4163575491175463</v>
@@ -4620,7 +4620,7 @@
         <v>0.0002911262085714918</v>
       </c>
       <c r="H102" t="n">
-        <v>0.3679956835249412</v>
+        <v>0.3679956835249405</v>
       </c>
       <c r="I102" t="n">
         <v>0.09670297537789491</v>
@@ -4629,10 +4629,10 @@
         <v>0.01318016778774229</v>
       </c>
       <c r="K102" t="n">
-        <v>6.54728362733105e-05</v>
+        <v>6.547283627395804e-05</v>
       </c>
       <c r="L102" t="n">
-        <v>0.004708132612224185</v>
+        <v>0.004708132612225482</v>
       </c>
       <c r="M102" t="n">
         <v>0.0041056676656675</v>
@@ -4661,7 +4661,7 @@
         <v>0.0006503811781559664</v>
       </c>
       <c r="H103" t="n">
-        <v>0.3079249779119051</v>
+        <v>0.3079249779119</v>
       </c>
       <c r="I103" t="n">
         <v>0.2379029221851333</v>
@@ -4670,10 +4670,10 @@
         <v>0.01480912293515087</v>
       </c>
       <c r="K103" t="n">
-        <v>0.0186389175249447</v>
+        <v>0.01863891752494995</v>
       </c>
       <c r="L103" t="n">
-        <v>0.005601740284645267</v>
+        <v>0.005601740284655726</v>
       </c>
       <c r="M103" t="n">
         <v>0.4287216583416553</v>
@@ -4702,7 +4702,7 @@
         <v>0.0002446918327238571</v>
       </c>
       <c r="H104" t="n">
-        <v>0.3472696301920578</v>
+        <v>0.347269630192056</v>
       </c>
       <c r="I104" t="n">
         <v>0.1280651445679143</v>
@@ -4711,10 +4711,10 @@
         <v>0.0137355957284803</v>
       </c>
       <c r="K104" t="n">
-        <v>0.003225565132175479</v>
+        <v>0.003225565132177287</v>
       </c>
       <c r="L104" t="n">
-        <v>0.00369517448417637</v>
+        <v>0.00369517448417994</v>
       </c>
       <c r="M104" t="n">
         <v>0.0050166433566431</v>
@@ -4743,7 +4743,7 @@
         <v>0.0002020351971319458</v>
       </c>
       <c r="H105" t="n">
-        <v>0.3726046031178552</v>
+        <v>0.3726046031178566</v>
       </c>
       <c r="I105" t="n">
         <v>0.06262581955425163</v>
@@ -4752,10 +4752,10 @@
         <v>0.01234081745709435</v>
       </c>
       <c r="K105" t="n">
-        <v>9.376747987336243e-06</v>
+        <v>9.376747986021238e-06</v>
       </c>
       <c r="L105" t="n">
-        <v>0.00432657857815277</v>
+        <v>0.004326578578150132</v>
       </c>
       <c r="M105" t="n">
         <v>0.0020096370296369</v>
@@ -4784,7 +4784,7 @@
         <v>0.0006763043951850218</v>
       </c>
       <c r="H106" t="n">
-        <v>0.3080753458740251</v>
+        <v>0.30807534587402</v>
       </c>
       <c r="I106" t="n">
         <v>0.2370985323303797</v>
@@ -4793,10 +4793,10 @@
         <v>0.01477866579605574</v>
       </c>
       <c r="K106" t="n">
-        <v>0.01856691972637346</v>
+        <v>0.0185669197263787</v>
       </c>
       <c r="L106" t="n">
-        <v>0.005609802979463193</v>
+        <v>0.00560980297947363</v>
       </c>
       <c r="M106" t="n">
         <v>0.4303892940392909</v>
@@ -4825,7 +4825,7 @@
         <v>0.0003920562613750673</v>
       </c>
       <c r="H107" t="n">
-        <v>0.3402686964244281</v>
+        <v>0.3402686964244269</v>
       </c>
       <c r="I107" t="n">
         <v>0.1790595780778723</v>
@@ -4834,10 +4834,10 @@
         <v>0.01393139793616125</v>
       </c>
       <c r="K107" t="n">
-        <v>0.001488895143115689</v>
+        <v>0.001488895143116909</v>
       </c>
       <c r="L107" t="n">
-        <v>0.002305320259547705</v>
+        <v>0.002305320259550128</v>
       </c>
       <c r="M107" t="n">
         <v>0.0228800666000662</v>
@@ -4866,7 +4866,7 @@
         <v>0.0002631001563420708</v>
       </c>
       <c r="H108" t="n">
-        <v>0.3697720479230609</v>
+        <v>0.3697720479230613</v>
       </c>
       <c r="I108" t="n">
         <v>0.08349857188721595</v>
@@ -4875,10 +4875,10 @@
         <v>0.01285037489117909</v>
       </c>
       <c r="K108" t="n">
-        <v>4.375512030337841e-05</v>
+        <v>4.375512030288374e-05</v>
       </c>
       <c r="L108" t="n">
-        <v>0.004483422716005498</v>
+        <v>0.004483422716004509</v>
       </c>
       <c r="M108" t="n">
         <v>0.0066801998001996</v>
@@ -4907,7 +4907,7 @@
         <v>0.0003645634772722238</v>
       </c>
       <c r="H109" t="n">
-        <v>0.3000082929365604</v>
+        <v>0.3000082929365603</v>
       </c>
       <c r="I109" t="n">
         <v>0.2547303088768357</v>
@@ -4916,10 +4916,10 @@
         <v>0.01541999235208664</v>
       </c>
       <c r="K109" t="n">
-        <v>0.02307632393767203</v>
+        <v>0.02307632393767219</v>
       </c>
       <c r="L109" t="n">
-        <v>0.004494085771090462</v>
+        <v>0.00449408577109069</v>
       </c>
       <c r="M109" t="n">
         <v>0.3179209057609053</v>
@@ -4957,10 +4957,10 @@
         <v>0.01536486717570163</v>
       </c>
       <c r="K110" t="n">
-        <v>0.02286284575927457</v>
+        <v>0.02286284575927473</v>
       </c>
       <c r="L110" t="n">
-        <v>0.00450411777948271</v>
+        <v>0.004504117779482944</v>
       </c>
       <c r="M110" t="n">
         <v>0.3208992640692634</v>
@@ -4989,7 +4989,7 @@
         <v>0.0001255472719778779</v>
       </c>
       <c r="H111" t="n">
-        <v>0.3678844865449367</v>
+        <v>0.3678844865449387</v>
       </c>
       <c r="I111" t="n">
         <v>0.1384771935916475</v>
@@ -4998,10 +4998,10 @@
         <v>0.01355509928533837</v>
       </c>
       <c r="K111" t="n">
-        <v>0.007397883461957324</v>
+        <v>0.007397883461955301</v>
       </c>
       <c r="L111" t="n">
-        <v>0.002983498972956533</v>
+        <v>0.002983498972952474</v>
       </c>
       <c r="M111" t="n">
         <v>0.0037409756909755</v>
@@ -5030,7 +5030,7 @@
         <v>0.000675740666061521</v>
       </c>
       <c r="H112" t="n">
-        <v>0.3078987558321017</v>
+        <v>0.3078987558320966</v>
       </c>
       <c r="I112" t="n">
         <v>0.2371886622750209</v>
@@ -5039,10 +5039,10 @@
         <v>0.01478201958152032</v>
       </c>
       <c r="K112" t="n">
-        <v>0.01860607575433027</v>
+        <v>0.01860607575433551</v>
       </c>
       <c r="L112" t="n">
-        <v>0.005607797045146606</v>
+        <v>0.005607797045157029</v>
       </c>
       <c r="M112" t="n">
         <v>0.4309572693972663</v>
@@ -5080,10 +5080,10 @@
         <v>0.01533228990366349</v>
       </c>
       <c r="K113" t="n">
-        <v>0.02263078698649443</v>
+        <v>0.02263078698649459</v>
       </c>
       <c r="L113" t="n">
-        <v>0.004523189205854723</v>
+        <v>0.004523189205854953</v>
       </c>
       <c r="M113" t="n">
         <v>0.3246402397602389</v>
@@ -5112,7 +5112,7 @@
         <v>0.0001981188093282807</v>
       </c>
       <c r="H114" t="n">
-        <v>0.3726045462416786</v>
+        <v>0.372604546241678</v>
       </c>
       <c r="I114" t="n">
         <v>0.06266763607259501</v>
@@ -5121,10 +5121,10 @@
         <v>0.01234473384489806</v>
       </c>
       <c r="K114" t="n">
-        <v>9.433624163988467e-06</v>
+        <v>9.43362416459635e-06</v>
       </c>
       <c r="L114" t="n">
-        <v>0.004372425236653132</v>
+        <v>0.004372425236654339</v>
       </c>
       <c r="M114" t="n">
         <v>0.0020878454878454</v>
@@ -5153,7 +5153,7 @@
         <v>0.0001582276154104416</v>
       </c>
       <c r="H115" t="n">
-        <v>0.3395696258367586</v>
+        <v>0.3395696258367582</v>
       </c>
       <c r="I115" t="n">
         <v>0.1351593426255357</v>
@@ -5162,10 +5162,10 @@
         <v>0.0137368224457544</v>
       </c>
       <c r="K115" t="n">
-        <v>0.003129363135671553</v>
+        <v>0.003129363135671963</v>
       </c>
       <c r="L115" t="n">
-        <v>0.004221534763835837</v>
+        <v>0.004221534763836688</v>
       </c>
       <c r="M115" t="n">
         <v>0.009965844155843701</v>
@@ -5194,7 +5194,7 @@
         <v>0.0006795003805315597</v>
       </c>
       <c r="H116" t="n">
-        <v>0.3079723652354265</v>
+        <v>0.3079723652354214</v>
       </c>
       <c r="I116" t="n">
         <v>0.2369980973622987</v>
@@ -5203,10 +5203,10 @@
         <v>0.01477492905559484</v>
       </c>
       <c r="K116" t="n">
-        <v>0.01858515442922787</v>
+        <v>0.0185851544292331</v>
       </c>
       <c r="L116" t="n">
-        <v>0.005611594421600398</v>
+        <v>0.005611594421610811</v>
       </c>
       <c r="M116" t="n">
         <v>0.4314502797202766</v>
@@ -5235,7 +5235,7 @@
         <v>0.0001760000399013256</v>
       </c>
       <c r="H117" t="n">
-        <v>0.3516987158667279</v>
+        <v>0.3516987158667268</v>
       </c>
       <c r="I117" t="n">
         <v>0.1143231058408564</v>
@@ -5244,10 +5244,10 @@
         <v>0.01340539728408641</v>
       </c>
       <c r="K117" t="n">
-        <v>0.001882482501343097</v>
+        <v>0.001882482501344143</v>
       </c>
       <c r="L117" t="n">
-        <v>0.004229419290835636</v>
+        <v>0.004229419290837745</v>
       </c>
       <c r="M117" t="n">
         <v>0.0166460439560433</v>
@@ -5285,10 +5285,10 @@
         <v>0.01531257972108674</v>
       </c>
       <c r="K118" t="n">
-        <v>0.02255562897799731</v>
+        <v>0.02255562897799748</v>
       </c>
       <c r="L118" t="n">
-        <v>0.004527200738804616</v>
+        <v>0.00452720073880487</v>
       </c>
       <c r="M118" t="n">
         <v>0.3257259740259731</v>
@@ -5317,7 +5317,7 @@
         <v>0.0008882657606169585</v>
       </c>
       <c r="H119" t="n">
-        <v>0.3635745065631649</v>
+        <v>0.363574506563164</v>
       </c>
       <c r="I119" t="n">
         <v>0.07937922772789323</v>
@@ -5326,10 +5326,10 @@
         <v>0.01255113495177197</v>
       </c>
       <c r="K119" t="n">
-        <v>0.002583878606308797</v>
+        <v>0.002583878606309641</v>
       </c>
       <c r="L119" t="n">
-        <v>0.005646714862622922</v>
+        <v>0.005646714862624631</v>
       </c>
       <c r="M119" t="n">
         <v>0.005117585747585599</v>
@@ -5358,7 +5358,7 @@
         <v>0.0006829158833672432</v>
       </c>
       <c r="H120" t="n">
-        <v>0.3080027113659728</v>
+        <v>0.3080027113659677</v>
       </c>
       <c r="I120" t="n">
         <v>0.2367400961229861</v>
@@ -5367,10 +5367,10 @@
         <v>0.01476578976785882</v>
       </c>
       <c r="K120" t="n">
-        <v>0.01849721603523658</v>
+        <v>0.01849721603524178</v>
       </c>
       <c r="L120" t="n">
-        <v>0.005634287955148577</v>
+        <v>0.005634287955158922</v>
       </c>
       <c r="M120" t="n">
         <v>0.4338734565434533</v>
@@ -5399,7 +5399,7 @@
         <v>0.0006959367122756106</v>
       </c>
       <c r="H121" t="n">
-        <v>0.3082560574869508</v>
+        <v>0.3082560574869457</v>
       </c>
       <c r="I121" t="n">
         <v>0.2360851151565348</v>
@@ -5408,10 +5408,10 @@
         <v>0.01474132067181424</v>
       </c>
       <c r="K121" t="n">
-        <v>0.01842554668589625</v>
+        <v>0.01842554668590144</v>
       </c>
       <c r="L121" t="n">
-        <v>0.005647537673305221</v>
+        <v>0.005647537673315541</v>
       </c>
       <c r="M121" t="n">
         <v>0.4355895604395572</v>
@@ -5440,7 +5440,7 @@
         <v>0.0004132007006688484</v>
       </c>
       <c r="H122" t="n">
-        <v>0.3018979919615821</v>
+        <v>0.301897991961582</v>
       </c>
       <c r="I122" t="n">
         <v>0.250809345156811</v>
@@ -5449,10 +5449,10 @@
         <v>0.01529994335594646</v>
       </c>
       <c r="K122" t="n">
-        <v>0.02250752275319689</v>
+        <v>0.02250752275319706</v>
       </c>
       <c r="L122" t="n">
-        <v>0.004529853452920027</v>
+        <v>0.004529853452920287</v>
       </c>
       <c r="M122" t="n">
         <v>0.3264247785547776</v>
@@ -5481,7 +5481,7 @@
         <v>0.000730712742549914</v>
       </c>
       <c r="H123" t="n">
-        <v>0.3097636720094135</v>
+        <v>0.3097636720094087</v>
       </c>
       <c r="I123" t="n">
         <v>0.2334550847507747</v>
@@ -5490,10 +5490,10 @@
         <v>0.01465095995373354</v>
       </c>
       <c r="K123" t="n">
-        <v>0.01767030391350934</v>
+        <v>0.01767030391351421</v>
       </c>
       <c r="L123" t="n">
-        <v>0.005826620414641721</v>
+        <v>0.005826620414651407</v>
       </c>
       <c r="M123" t="n">
         <v>0.4584696270396234</v>
@@ -5522,7 +5522,7 @@
         <v>0.0007462013195250661</v>
       </c>
       <c r="H124" t="n">
-        <v>0.3100468321177791</v>
+        <v>0.3100468321177744</v>
       </c>
       <c r="I124" t="n">
         <v>0.2327207307078352</v>
@@ -5531,10 +5531,10 @@
         <v>0.01462260215202714</v>
       </c>
       <c r="K124" t="n">
-        <v>0.01759195834621583</v>
+        <v>0.01759195834622066</v>
       </c>
       <c r="L124" t="n">
-        <v>0.005845434868635051</v>
+        <v>0.005845434868644667</v>
       </c>
       <c r="M124" t="n">
         <v>0.4605574725274688</v>
@@ -5563,7 +5563,7 @@
         <v>0.0007521061650283086</v>
       </c>
       <c r="H125" t="n">
-        <v>0.3101542802785578</v>
+        <v>0.3101542802785532</v>
       </c>
       <c r="I125" t="n">
         <v>0.232442119392838</v>
@@ -5572,10 +5572,10 @@
         <v>0.01461181335978329</v>
       </c>
       <c r="K125" t="n">
-        <v>0.01756223851260411</v>
+        <v>0.01756223851260894</v>
       </c>
       <c r="L125" t="n">
-        <v>0.005852654147506692</v>
+        <v>0.005852654147516284</v>
       </c>
       <c r="M125" t="n">
         <v>0.4613548085248046</v>
@@ -5604,7 +5604,7 @@
         <v>0.0004501491141572942</v>
       </c>
       <c r="H126" t="n">
-        <v>0.3028762182290536</v>
+        <v>0.3028762182290535</v>
       </c>
       <c r="I126" t="n">
         <v>0.2482719828056657</v>
@@ -5613,10 +5613,10 @@
         <v>0.01522789814100833</v>
       </c>
       <c r="K126" t="n">
-        <v>0.02217378092501974</v>
+        <v>0.02217378092501989</v>
       </c>
       <c r="L126" t="n">
-        <v>0.004573844433197017</v>
+        <v>0.004573844433197249</v>
       </c>
       <c r="M126" t="n">
         <v>0.3315423643023632</v>
@@ -5645,7 +5645,7 @@
         <v>0.001965886672138816</v>
       </c>
       <c r="H127" t="n">
-        <v>0.2975923835032087</v>
+        <v>0.2975923835032065</v>
       </c>
       <c r="I127" t="n">
         <v>0.2320881929548722</v>
@@ -5654,10 +5654,10 @@
         <v>0.01352938235672406</v>
       </c>
       <c r="K127" t="n">
-        <v>0.02900915562194335</v>
+        <v>0.02900915562194558</v>
       </c>
       <c r="L127" t="n">
-        <v>0.01604214839376236</v>
+        <v>0.01604214839376667</v>
       </c>
       <c r="M127" t="n">
         <v>0.7928971728271679</v>
@@ -5686,7 +5686,7 @@
         <v>0.001970597317334818</v>
       </c>
       <c r="H128" t="n">
-        <v>0.2978265217332078</v>
+        <v>0.2978265217332062</v>
       </c>
       <c r="I128" t="n">
         <v>0.2315424398291656</v>
@@ -5695,10 +5695,10 @@
         <v>0.01351521802240231</v>
       </c>
       <c r="K128" t="n">
-        <v>0.02892235003594942</v>
+        <v>0.02892235003595105</v>
       </c>
       <c r="L128" t="n">
-        <v>0.0160032492085741</v>
+        <v>0.01600324920857722</v>
       </c>
       <c r="M128" t="n">
         <v>0.7954441991341941</v>
@@ -5727,7 +5727,7 @@
         <v>0.001954274213843228</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2981113853611164</v>
+        <v>0.2981113853611148</v>
       </c>
       <c r="I129" t="n">
         <v>0.2309915695673394</v>
@@ -5736,10 +5736,10 @@
         <v>0.01352077137120551</v>
       </c>
       <c r="K129" t="n">
-        <v>0.02876735474013837</v>
+        <v>0.02876735474013998</v>
       </c>
       <c r="L129" t="n">
-        <v>0.01594724882169653</v>
+        <v>0.01594724882169963</v>
       </c>
       <c r="M129" t="n">
         <v>0.80053487512487</v>
@@ -5768,7 +5768,7 @@
         <v>0.000148724349132064</v>
       </c>
       <c r="H130" t="n">
-        <v>0.3547044928226198</v>
+        <v>0.3547044928226192</v>
       </c>
       <c r="I130" t="n">
         <v>0.1031274071633658</v>
@@ -5777,10 +5777,10 @@
         <v>0.01299236265909195</v>
       </c>
       <c r="K130" t="n">
-        <v>3.642789704412123e-05</v>
+        <v>3.642789704477516e-05</v>
       </c>
       <c r="L130" t="n">
-        <v>0.004540151608019331</v>
+        <v>0.004540151608020668</v>
       </c>
       <c r="M130" t="n">
         <v>0.0035856576756576</v>
@@ -5809,7 +5809,7 @@
         <v>0.000161259143113724</v>
       </c>
       <c r="H131" t="n">
-        <v>0.3452698355730281</v>
+        <v>0.3452698355730272</v>
       </c>
       <c r="I131" t="n">
         <v>0.129486064957254</v>
@@ -5818,10 +5818,10 @@
         <v>0.01367231644452454</v>
       </c>
       <c r="K131" t="n">
-        <v>0.004184486327618446</v>
+        <v>0.00418448632761939</v>
       </c>
       <c r="L131" t="n">
-        <v>0.00390642428204808</v>
+        <v>0.003906424282049993</v>
       </c>
       <c r="M131" t="n">
         <v>0.018193589743589</v>
@@ -5850,7 +5850,7 @@
         <v>0.001962719007241097</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2982885612566282</v>
+        <v>0.2982885612566266</v>
       </c>
       <c r="I132" t="n">
         <v>0.2306479899273803</v>
@@ -5859,10 +5859,10 @@
         <v>0.01350498412713658</v>
       </c>
       <c r="K132" t="n">
-        <v>0.02870470362175513</v>
+        <v>0.02870470362175674</v>
       </c>
       <c r="L132" t="n">
-        <v>0.01600206154144954</v>
+        <v>0.01600206154145263</v>
       </c>
       <c r="M132" t="n">
         <v>0.8025445121545068</v>
@@ -5891,7 +5891,7 @@
         <v>0.001965697357828347</v>
       </c>
       <c r="H133" t="n">
-        <v>0.2983509700318659</v>
+        <v>0.2983509700318643</v>
       </c>
       <c r="I133" t="n">
         <v>0.2305270878461387</v>
@@ -5900,10 +5900,10 @@
         <v>0.01349941794498441</v>
       </c>
       <c r="K133" t="n">
-        <v>0.02868265886753667</v>
+        <v>0.02868265886753828</v>
       </c>
       <c r="L133" t="n">
-        <v>0.01602164302941327</v>
+        <v>0.01602164302941636</v>
       </c>
       <c r="M133" t="n">
         <v>0.8032552114552062</v>
@@ -5932,7 +5932,7 @@
         <v>0.001968620506921805</v>
       </c>
       <c r="H134" t="n">
-        <v>0.2984122039612807</v>
+        <v>0.2984122039612792</v>
       </c>
       <c r="I134" t="n">
         <v>0.2304085068588186</v>
@@ -5941,10 +5941,10 @@
         <v>0.01349395514839716</v>
       </c>
       <c r="K134" t="n">
-        <v>0.02866103740216723</v>
+        <v>0.02866103740216883</v>
       </c>
       <c r="L134" t="n">
-        <v>0.01604095528092631</v>
+        <v>0.0160409552809294</v>
       </c>
       <c r="M134" t="n">
         <v>0.8039539027638974</v>
@@ -5973,7 +5973,7 @@
         <v>0.001971256022969672</v>
       </c>
       <c r="H135" t="n">
-        <v>0.2984673977927504</v>
+        <v>0.2984673977927489</v>
       </c>
       <c r="I135" t="n">
         <v>0.2303016633647934</v>
@@ -5982,10 +5982,10 @@
         <v>0.01348903002083429</v>
       </c>
       <c r="K135" t="n">
-        <v>0.02864155606782061</v>
+        <v>0.02864155606782222</v>
       </c>
       <c r="L135" t="n">
-        <v>0.01605845172408015</v>
+        <v>0.01605845172408325</v>
       </c>
       <c r="M135" t="n">
         <v>0.8045848484848431</v>
@@ -6014,7 +6014,7 @@
         <v>0.001991087905460454</v>
       </c>
       <c r="H136" t="n">
-        <v>0.2988825414656903</v>
+        <v>0.2988825414656888</v>
       </c>
       <c r="I136" t="n">
         <v>0.2294982369998433</v>
@@ -6023,10 +6023,10 @@
         <v>0.01345197350271197</v>
       </c>
       <c r="K136" t="n">
-        <v>0.0284950757669888</v>
+        <v>0.0284950757669904</v>
       </c>
       <c r="L136" t="n">
-        <v>0.01619057726385205</v>
+        <v>0.01619057726385514</v>
       </c>
       <c r="M136" t="n">
         <v>0.8093633599733545</v>
@@ -6055,7 +6055,7 @@
         <v>0.001991249189434891</v>
       </c>
       <c r="H137" t="n">
-        <v>0.2988985580625254</v>
+        <v>0.2988985580625239</v>
       </c>
       <c r="I137" t="n">
         <v>0.2294975215410789</v>
@@ -6064,10 +6064,10 @@
         <v>0.01345191838531921</v>
       </c>
       <c r="K137" t="n">
-        <v>0.02851075900481643</v>
+        <v>0.02851075900481802</v>
       </c>
       <c r="L137" t="n">
-        <v>0.01619770866489779</v>
+        <v>0.01619770866490088</v>
       </c>
       <c r="M137" t="n">
         <v>0.809852820512815</v>
@@ -6096,7 +6096,7 @@
         <v>0.002004968381898577</v>
       </c>
       <c r="H138" t="n">
-        <v>0.2992519856512214</v>
+        <v>0.2992519856512198</v>
       </c>
       <c r="I138" t="n">
         <v>0.2289545488479352</v>
@@ -6105,10 +6105,10 @@
         <v>0.01342571157337829</v>
       </c>
       <c r="K138" t="n">
-        <v>0.0283999328007818</v>
+        <v>0.02839993280078338</v>
       </c>
       <c r="L138" t="n">
-        <v>0.0163019381678287</v>
+        <v>0.01630193816783177</v>
       </c>
       <c r="M138" t="n">
         <v>0.8141089410589354</v>
@@ -6137,7 +6137,7 @@
         <v>0.0005115298853741449</v>
       </c>
       <c r="H139" t="n">
-        <v>0.3628035285826315</v>
+        <v>0.3628035285826314</v>
       </c>
       <c r="I139" t="n">
         <v>0.04738164194198288</v>
@@ -6146,10 +6146,10 @@
         <v>0.01269439358100396</v>
       </c>
       <c r="K139" t="n">
-        <v>6.294297926337898e-06</v>
+        <v>6.294297926500344e-06</v>
       </c>
       <c r="L139" t="n">
-        <v>0.004985940919460796</v>
+        <v>0.004985940919461126</v>
       </c>
       <c r="M139" t="n">
         <v>0.0042752047952047</v>
@@ -6178,7 +6178,7 @@
         <v>0.00043681915742825</v>
       </c>
       <c r="H140" t="n">
-        <v>0.3653126077274882</v>
+        <v>0.3653126077274884</v>
       </c>
       <c r="I140" t="n">
         <v>0.05125727561438689</v>
@@ -6187,10 +6187,10 @@
         <v>0.0125993604035854</v>
       </c>
       <c r="K140" t="n">
-        <v>7.046478758667458e-06</v>
+        <v>7.046478758494656e-06</v>
       </c>
       <c r="L140" t="n">
-        <v>0.004785728963857003</v>
+        <v>0.004785728963856623</v>
       </c>
       <c r="M140" t="n">
         <v>0.0057462171162169</v>
@@ -6219,7 +6219,7 @@
         <v>0.002052368246815386</v>
       </c>
       <c r="H141" t="n">
-        <v>0.3000961381053049</v>
+        <v>0.3000961381053034</v>
       </c>
       <c r="I141" t="n">
         <v>0.2272910610573453</v>
@@ -6228,10 +6228,10 @@
         <v>0.01334340005005946</v>
       </c>
       <c r="K141" t="n">
-        <v>0.02803236664685802</v>
+        <v>0.02803236664685957</v>
       </c>
       <c r="L141" t="n">
-        <v>0.01677764187070491</v>
+        <v>0.01677764187070791</v>
       </c>
       <c r="M141" t="n">
         <v>0.8323025308025244</v>
@@ -6260,7 +6260,7 @@
         <v>0.002076808538625211</v>
       </c>
       <c r="H142" t="n">
-        <v>0.3005170226708384</v>
+        <v>0.3005170226708368</v>
       </c>
       <c r="I142" t="n">
         <v>0.2264028732296773</v>
@@ -6269,10 +6269,10 @@
         <v>0.01330278085551288</v>
       </c>
       <c r="K142" t="n">
-        <v>0.02786648922750268</v>
+        <v>0.02786648922750422</v>
       </c>
       <c r="L142" t="n">
-        <v>0.01703128163721617</v>
+        <v>0.01703128163721915</v>
       </c>
       <c r="M142" t="n">
         <v>0.8380487479187413</v>
@@ -6301,7 +6301,7 @@
         <v>0.002088085346442703</v>
       </c>
       <c r="H143" t="n">
-        <v>0.3007153651001646</v>
+        <v>0.300715365100163</v>
       </c>
       <c r="I143" t="n">
         <v>0.2259885006956547</v>
@@ -6310,10 +6310,10 @@
         <v>0.01328196724263053</v>
       </c>
       <c r="K143" t="n">
-        <v>0.02778043860162755</v>
+        <v>0.02778043860162908</v>
       </c>
       <c r="L143" t="n">
-        <v>0.01713442848449426</v>
+        <v>0.01713442848449722</v>
       </c>
       <c r="M143" t="n">
         <v>0.8416344055943988</v>
@@ -6423,7 +6423,7 @@
         <v>4.690176637852188e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3416610353205169</v>
+        <v>0.3416610353205165</v>
       </c>
       <c r="I2" t="n">
         <v>0.2196784194275986</v>
@@ -6432,10 +6432,10 @@
         <v>0.01465924588410717</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0003653612160858422</v>
+        <v>0.0003653612160861185</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002038647920528116</v>
+        <v>0.002038647920528673</v>
       </c>
       <c r="M2" t="n">
         <v>0.0188563336663336</v>
@@ -6464,7 +6464,7 @@
         <v>0.0004334210901345925</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3262455237200253</v>
+        <v>0.3262455237200259</v>
       </c>
       <c r="I3" t="n">
         <v>0.2208410240428516</v>
@@ -6473,10 +6473,10 @@
         <v>0.01460303822972621</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005399670836509782</v>
+        <v>0.000539967083650392</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002973217385431635</v>
+        <v>0.00297321738543037</v>
       </c>
       <c r="M3" t="n">
         <v>0.0085793439893439</v>
@@ -6505,7 +6505,7 @@
         <v>0.0001223274887467285</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3740051337165698</v>
+        <v>0.3740051337165704</v>
       </c>
       <c r="I4" t="n">
         <v>0.1120983705142947</v>
@@ -6514,10 +6514,10 @@
         <v>0.01303273371683093</v>
       </c>
       <c r="K4" t="n">
-        <v>4.461694946514964e-05</v>
+        <v>4.461694946451179e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004421415426009026</v>
+        <v>0.004421415426007726</v>
       </c>
       <c r="M4" t="n">
         <v>0.0043271361971361</v>
@@ -6546,7 +6546,7 @@
         <v>0.001712670414148174</v>
       </c>
       <c r="H5" t="n">
-        <v>0.254065293531252</v>
+        <v>0.2540652935312515</v>
       </c>
       <c r="I5" t="n">
         <v>0.1647800187101549</v>
@@ -6555,10 +6555,10 @@
         <v>0.01486860820920242</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02021468367476486</v>
+        <v>0.02021468367476531</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008739186398563021</v>
+        <v>0.008739186398563928</v>
       </c>
       <c r="M5" t="n">
         <v>0.001399587079587</v>
@@ -6587,7 +6587,7 @@
         <v>4.768297232604557e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3000176486878958</v>
+        <v>0.3000176486878959</v>
       </c>
       <c r="I6" t="n">
         <v>0.2748486497270107</v>
@@ -6599,7 +6599,7 @@
         <v>0.01585505978827974</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008997463192917458</v>
+        <v>0.0008997463192917388</v>
       </c>
       <c r="M6" t="n">
         <v>0.1264290775890775</v>
@@ -6628,7 +6628,7 @@
         <v>5.624896519441697e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3425299763889501</v>
+        <v>0.3425299763889496</v>
       </c>
       <c r="I7" t="n">
         <v>0.2152442658787091</v>
@@ -6637,10 +6637,10 @@
         <v>0.01458915316146854</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003553223200422136</v>
+        <v>0.0003553223200425702</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002073714548229568</v>
+        <v>0.002073714548230286</v>
       </c>
       <c r="M7" t="n">
         <v>0.0194011188811188</v>
@@ -6669,7 +6669,7 @@
         <v>0.0004032100258753509</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3344587270105278</v>
+        <v>0.3344587270105283</v>
       </c>
       <c r="I8" t="n">
         <v>0.1927317932019531</v>
@@ -6678,10 +6678,10 @@
         <v>0.01419147600396591</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0004458479569160475</v>
+        <v>0.0004458479569156108</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003122514536437881</v>
+        <v>0.003122514536436931</v>
       </c>
       <c r="M8" t="n">
         <v>0.0104265334665333</v>
@@ -6710,7 +6710,7 @@
         <v>0.0003947609925461306</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3371211494873653</v>
+        <v>0.3371211494873656</v>
       </c>
       <c r="I9" t="n">
         <v>0.183615257677862</v>
@@ -6719,10 +6719,10 @@
         <v>0.01405671864139761</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0004153292355781133</v>
+        <v>0.0004153292355778881</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003164976145283023</v>
+        <v>0.003164976145282511</v>
       </c>
       <c r="M9" t="n">
         <v>0.0112088478188476</v>
@@ -6751,7 +6751,7 @@
         <v>7.599158366338613e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2504318517969096</v>
+        <v>0.2504318517969091</v>
       </c>
       <c r="I10" t="n">
         <v>0.227383877063066</v>
@@ -6760,10 +6760,10 @@
         <v>0.01570208583435296</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02552541959340105</v>
+        <v>0.02552541959340146</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001786089930115507</v>
+        <v>0.001786089930116308</v>
       </c>
       <c r="M10" t="n">
         <v>0.0051407992007991</v>
@@ -6801,10 +6801,10 @@
         <v>0.01589412570439603</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01585147101978365</v>
+        <v>0.01585147101978363</v>
       </c>
       <c r="L11" t="n">
-        <v>0.000886601488398577</v>
+        <v>0.0008866014883985446</v>
       </c>
       <c r="M11" t="n">
         <v>0.1343125274725273</v>
@@ -6833,7 +6833,7 @@
         <v>5.056479573502324e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3226289903650763</v>
+        <v>0.3226289903650765</v>
       </c>
       <c r="I12" t="n">
         <v>0.2298246171588506</v>
@@ -6842,10 +6842,10 @@
         <v>0.01489153460532486</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0007106350782891503</v>
+        <v>0.0007106350782889127</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001770188407292079</v>
+        <v>0.001770188407291616</v>
       </c>
       <c r="M12" t="n">
         <v>0.0176287279387278</v>
@@ -6874,7 +6874,7 @@
         <v>0.0001099550105078655</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2776703089497444</v>
+        <v>0.277670308949744</v>
       </c>
       <c r="I13" t="n">
         <v>0.1906012114137966</v>
@@ -6883,10 +6883,10 @@
         <v>0.01494682977424574</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01983655385045388</v>
+        <v>0.01983655385045421</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002296596016259886</v>
+        <v>0.002296596016260592</v>
       </c>
       <c r="M13" t="n">
         <v>0.0066157875457874</v>
@@ -6915,7 +6915,7 @@
         <v>9.188510595746458e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3395308147405143</v>
+        <v>0.3395308147405133</v>
       </c>
       <c r="I14" t="n">
         <v>0.1374307116650175</v>
@@ -6924,10 +6924,10 @@
         <v>0.01355693152053916</v>
       </c>
       <c r="K14" t="n">
-        <v>4.099802503228046e-05</v>
+        <v>4.099802503317829e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.004625287662623117</v>
+        <v>0.004625287662624922</v>
       </c>
       <c r="M14" t="n">
         <v>0.0062348418248417</v>
@@ -6956,7 +6956,7 @@
         <v>0.000100099575349515</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3022047220497404</v>
+        <v>0.3022047220497415</v>
       </c>
       <c r="I15" t="n">
         <v>0.1550780308140488</v>
@@ -6965,10 +6965,10 @@
         <v>0.01539846382753333</v>
       </c>
       <c r="K15" t="n">
-        <v>3.423877380050153e-05</v>
+        <v>3.423877379941261e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.006647373868056148</v>
+        <v>0.006647373868053964</v>
       </c>
       <c r="M15" t="n">
         <v>0.0025251048951048</v>
@@ -6997,7 +6997,7 @@
         <v>4.62598941337561e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2990197401366982</v>
+        <v>0.2990197401366983</v>
       </c>
       <c r="I16" t="n">
         <v>0.2753947628044093</v>
@@ -7006,10 +7006,10 @@
         <v>0.01590434581078662</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01607062358122479</v>
+        <v>0.01607062358122477</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0008823877206483179</v>
+        <v>0.0008823877206482773</v>
       </c>
       <c r="M16" t="n">
         <v>0.1362522444222442</v>
@@ -7038,7 +7038,7 @@
         <v>0.0001994239929334641</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3726045665945562</v>
+        <v>0.3726045665945538</v>
       </c>
       <c r="I17" t="n">
         <v>0.06265307686589072</v>
@@ -7047,10 +7047,10 @@
         <v>0.01234342866129283</v>
       </c>
       <c r="K17" t="n">
-        <v>9.413271286397998e-06</v>
+        <v>9.413271288824177e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004356520140588428</v>
+        <v>0.004356520140593279</v>
       </c>
       <c r="M17" t="n">
         <v>0.0017446586746586</v>
@@ -7079,7 +7079,7 @@
         <v>0.0002074623836542604</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3726046812105001</v>
+        <v>0.3726046812105014</v>
       </c>
       <c r="I18" t="n">
         <v>0.06256855041330669</v>
@@ -7088,10 +7088,10 @@
         <v>0.01233539027057214</v>
       </c>
       <c r="K18" t="n">
-        <v>9.298655342546295e-06</v>
+        <v>9.298655341187209e-06</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004263726065396014</v>
+        <v>0.004263726065393205</v>
       </c>
       <c r="M18" t="n">
         <v>0.0026689843489843</v>
@@ -7170,10 +7170,10 @@
         <v>0.01584226554092709</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01588771514054375</v>
+        <v>0.01588771514054372</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0009076481278800467</v>
+        <v>0.0009076481278799985</v>
       </c>
       <c r="M20" t="n">
         <v>0.1378213353313351</v>
@@ -7202,7 +7202,7 @@
         <v>0.0001237592320436766</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2875346750229932</v>
+        <v>0.2875346750229928</v>
       </c>
       <c r="I21" t="n">
         <v>0.1772727540807886</v>
@@ -7211,10 +7211,10 @@
         <v>0.01467181083593605</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01777633016982021</v>
+        <v>0.01777633016982052</v>
       </c>
       <c r="L21" t="n">
-        <v>0.002472259323186823</v>
+        <v>0.002472259323187467</v>
       </c>
       <c r="M21" t="n">
         <v>0.0073829237429235</v>
@@ -7243,7 +7243,7 @@
         <v>0.0001173494709432257</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3379956121777364</v>
+        <v>0.337995612177736</v>
       </c>
       <c r="I22" t="n">
         <v>0.2168160203806611</v>
@@ -7252,10 +7252,10 @@
         <v>0.01458124020140075</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0004122303500539929</v>
+        <v>0.0004122303500543476</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001305773671729299</v>
+        <v>0.00130577367173012</v>
       </c>
       <c r="M22" t="n">
         <v>0.0404135864135863</v>
@@ -7284,7 +7284,7 @@
         <v>0.0001539075530307024</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3401398459381424</v>
+        <v>0.3401398459381417</v>
       </c>
       <c r="I23" t="n">
         <v>0.2071848581742304</v>
@@ -7293,10 +7293,10 @@
         <v>0.01441113325581601</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0003870819547623977</v>
+        <v>0.0003870819547630022</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001382208295846414</v>
+        <v>0.001382208295847727</v>
       </c>
       <c r="M23" t="n">
         <v>0.0430825707625706</v>
@@ -7325,7 +7325,7 @@
         <v>8.497682780468585e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3281006429226589</v>
+        <v>0.3281006429226592</v>
       </c>
       <c r="I24" t="n">
         <v>0.2114242306466552</v>
@@ -7334,10 +7334,10 @@
         <v>0.01459444541391191</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0006336954510263879</v>
+        <v>0.0006336954510261088</v>
       </c>
       <c r="L24" t="n">
-        <v>0.001936983539801997</v>
+        <v>0.00193698353980145</v>
       </c>
       <c r="M24" t="n">
         <v>0.0197960639360637</v>
@@ -7366,7 +7366,7 @@
         <v>3.562581964112029e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3443432131494465</v>
+        <v>0.3443432131494469</v>
       </c>
       <c r="I25" t="n">
         <v>0.2340275388848566</v>
@@ -7375,10 +7375,10 @@
         <v>0.01488653192981008</v>
       </c>
       <c r="K25" t="n">
-        <v>0.002577263010741483</v>
+        <v>0.002577263010741205</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001526197285045769</v>
+        <v>0.001526197285045213</v>
       </c>
       <c r="M25" t="n">
         <v>0.007550506160505999</v>
@@ -7416,10 +7416,10 @@
         <v>0.01584124429970095</v>
       </c>
       <c r="K26" t="n">
-        <v>0.01591021415164941</v>
+        <v>0.01591021415164939</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0009068206942532303</v>
+        <v>0.0009068206942531827</v>
       </c>
       <c r="M26" t="n">
         <v>0.138374382284382</v>
@@ -7457,10 +7457,10 @@
         <v>0.01233044416221395</v>
       </c>
       <c r="K27" t="n">
-        <v>9.236872315588509e-06</v>
+        <v>9.236872315596541e-06</v>
       </c>
       <c r="L27" t="n">
-        <v>0.004213885451311839</v>
+        <v>0.004213885451311857</v>
       </c>
       <c r="M27" t="n">
         <v>0.0026559507159506</v>
@@ -7498,10 +7498,10 @@
         <v>0.01439657402385762</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0005830024083841171</v>
+        <v>0.0005830024083840403</v>
       </c>
       <c r="L28" t="n">
-        <v>0.00204491265440179</v>
+        <v>0.002044912654401657</v>
       </c>
       <c r="M28" t="n">
         <v>0.0215407226107223</v>
@@ -7539,10 +7539,10 @@
         <v>0.01584730848336176</v>
       </c>
       <c r="K29" t="n">
-        <v>0.01599765108002525</v>
+        <v>0.01599765108002523</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0009054704582724536</v>
+        <v>0.0009054704582724071</v>
       </c>
       <c r="M29" t="n">
         <v>0.1388655677655674</v>
@@ -7571,7 +7571,7 @@
         <v>8.627710803814364e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2700500550309688</v>
+        <v>0.2700500550309684</v>
       </c>
       <c r="I30" t="n">
         <v>0.2009624341916648</v>
@@ -7580,10 +7580,10 @@
         <v>0.01517162804100453</v>
       </c>
       <c r="K30" t="n">
-        <v>0.02144806530498035</v>
+        <v>0.02144806530498086</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0023239836744654</v>
+        <v>0.002323983674466418</v>
       </c>
       <c r="M30" t="n">
         <v>0.0014294505494504</v>
@@ -7612,7 +7612,7 @@
         <v>0.001466503353221726</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3562839908489099</v>
+        <v>0.3562839908489108</v>
       </c>
       <c r="I31" t="n">
         <v>0.04147179844690708</v>
@@ -7621,10 +7621,10 @@
         <v>0.01218037587476619</v>
       </c>
       <c r="K31" t="n">
-        <v>5.865489373373716e-06</v>
+        <v>5.865489372524226e-06</v>
       </c>
       <c r="L31" t="n">
-        <v>0.008906368450469855</v>
+        <v>0.008906368450468157</v>
       </c>
       <c r="M31" t="n">
         <v>0.0018187246087245</v>
@@ -7653,7 +7653,7 @@
         <v>0.0001199910725252128</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3330741474710967</v>
+        <v>0.3330741474710968</v>
       </c>
       <c r="I32" t="n">
         <v>0.1946965501820144</v>
@@ -7662,10 +7662,10 @@
         <v>0.01432066926303541</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0005637460713274116</v>
+        <v>0.0005637460713272196</v>
       </c>
       <c r="L32" t="n">
-        <v>0.002082284448800548</v>
+        <v>0.002082284448800184</v>
       </c>
       <c r="M32" t="n">
         <v>0.022286593406593</v>
@@ -7694,7 +7694,7 @@
         <v>0.0001481549814887075</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3409494601203697</v>
+        <v>0.3409494601203691</v>
       </c>
       <c r="I33" t="n">
         <v>0.2096156876420318</v>
@@ -7703,10 +7703,10 @@
         <v>0.01445811419146253</v>
       </c>
       <c r="K33" t="n">
-        <v>0.001115220893788906</v>
+        <v>0.001115220893789452</v>
       </c>
       <c r="L33" t="n">
-        <v>0.001341457975948589</v>
+        <v>0.001341457975949787</v>
       </c>
       <c r="M33" t="n">
         <v>0.0448369463869462</v>
@@ -7735,7 +7735,7 @@
         <v>8.687510639677087e-05</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3656533985091979</v>
+        <v>0.365653398509196</v>
       </c>
       <c r="I34" t="n">
         <v>0.1742352695812581</v>
@@ -7744,10 +7744,10 @@
         <v>0.01412977899517624</v>
       </c>
       <c r="K34" t="n">
-        <v>0.01088603329310545</v>
+        <v>0.01088603329310727</v>
       </c>
       <c r="L34" t="n">
-        <v>0.002393334720925446</v>
+        <v>0.002393334720929086</v>
       </c>
       <c r="M34" t="n">
         <v>0.0016962237762237</v>
@@ -7776,7 +7776,7 @@
         <v>6.910207365423685e-05</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3436998526587411</v>
+        <v>0.3436998526587406</v>
       </c>
       <c r="I35" t="n">
         <v>0.2092734640414093</v>
@@ -7785,10 +7785,10 @@
         <v>0.01449451704444369</v>
       </c>
       <c r="K35" t="n">
-        <v>0.000341804565259106</v>
+        <v>0.0003418045652595589</v>
       </c>
       <c r="L35" t="n">
-        <v>0.002119647085204468</v>
+        <v>0.002119647085205378</v>
       </c>
       <c r="M35" t="n">
         <v>0.0201863070263069</v>
@@ -7817,7 +7817,7 @@
         <v>9.437445169015531e-05</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2999661448187015</v>
+        <v>0.2999661448187016</v>
       </c>
       <c r="I36" t="n">
         <v>0.2712830090491948</v>
@@ -7826,10 +7826,10 @@
         <v>0.0158132119800224</v>
       </c>
       <c r="K36" t="n">
-        <v>0.01588555974178722</v>
+        <v>0.01588555974178715</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0009228810310171707</v>
+        <v>0.0009228810310170343</v>
       </c>
       <c r="M36" t="n">
         <v>0.139846603396603</v>
@@ -7858,7 +7858,7 @@
         <v>7.275705811252072e-05</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3138408071501831</v>
+        <v>0.3138408071501835</v>
       </c>
       <c r="I37" t="n">
         <v>0.1916858674085372</v>
@@ -7867,10 +7867,10 @@
         <v>0.01469285073263379</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01424315190502162</v>
+        <v>0.01424315190502126</v>
       </c>
       <c r="L37" t="n">
-        <v>0.002811204774798906</v>
+        <v>0.00281120477479817</v>
       </c>
       <c r="M37" t="n">
         <v>0.0073384948384947</v>
@@ -7899,7 +7899,7 @@
         <v>0.0001217598063328885</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3013197914879346</v>
+        <v>0.3013197914879348</v>
       </c>
       <c r="I38" t="n">
         <v>0.2674017044245492</v>
@@ -7908,10 +7908,10 @@
         <v>0.01572311499792182</v>
       </c>
       <c r="K38" t="n">
-        <v>0.01558984362457191</v>
+        <v>0.01558984362457179</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0009689364602944077</v>
+        <v>0.0009689364602941614</v>
       </c>
       <c r="M38" t="n">
         <v>0.1425025541125536</v>
@@ -7940,7 +7940,7 @@
         <v>0.0001024848588210497</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3307490255294232</v>
+        <v>0.3307490255294233</v>
       </c>
       <c r="I39" t="n">
         <v>0.1987925220942465</v>
@@ -7949,10 +7949,10 @@
         <v>0.01441866891537288</v>
       </c>
       <c r="K39" t="n">
-        <v>0.001513090859845718</v>
+        <v>0.001513090859845561</v>
       </c>
       <c r="L39" t="n">
-        <v>0.002231986349170309</v>
+        <v>0.00223198634917001</v>
       </c>
       <c r="M39" t="n">
         <v>0.0296250882450877</v>
@@ -7981,7 +7981,7 @@
         <v>9.646865923897898e-05</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3461129967894128</v>
+        <v>0.346112996789412</v>
       </c>
       <c r="I40" t="n">
         <v>0.1969524435627766</v>
@@ -7990,10 +7990,10 @@
         <v>0.01429845447654389</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0003139118336303985</v>
+        <v>0.0003139118336311419</v>
       </c>
       <c r="L40" t="n">
-        <v>0.002208631548717555</v>
+        <v>0.002208631548719046</v>
       </c>
       <c r="M40" t="n">
         <v>0.0220249783549782</v>
@@ -8022,7 +8022,7 @@
         <v>0.0002348702734721295</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3405750555536852</v>
+        <v>0.3405750555536831</v>
       </c>
       <c r="I41" t="n">
         <v>0.1462722657374163</v>
@@ -8031,10 +8031,10 @@
         <v>0.01429221341649623</v>
       </c>
       <c r="K41" t="n">
-        <v>0.01074819202519558</v>
+        <v>0.01074819202519764</v>
       </c>
       <c r="L41" t="n">
-        <v>0.003314011771038802</v>
+        <v>0.003314011771042915</v>
       </c>
       <c r="M41" t="n">
         <v>0.0045194039294037</v>
@@ -8063,7 +8063,7 @@
         <v>6.767321705609249e-05</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3643083955553857</v>
+        <v>0.3643083955553855</v>
       </c>
       <c r="I42" t="n">
         <v>0.1958351709136191</v>
@@ -8072,10 +8072,10 @@
         <v>0.01447327597732103</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01299158332497806</v>
+        <v>0.01299158332497814</v>
       </c>
       <c r="L42" t="n">
-        <v>0.001987942942368081</v>
+        <v>0.001987942942368311</v>
       </c>
       <c r="M42" t="n">
         <v>0.0015602997002996</v>
@@ -8104,7 +8104,7 @@
         <v>0.0005982685739036539</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3520074404468621</v>
+        <v>0.3520074404468618</v>
       </c>
       <c r="I43" t="n">
         <v>0.2367752239214622</v>
@@ -8113,10 +8113,10 @@
         <v>0.01461669539959872</v>
       </c>
       <c r="K43" t="n">
-        <v>0.003508289313543863</v>
+        <v>0.003508289313544187</v>
       </c>
       <c r="L43" t="n">
-        <v>0.001714159302167999</v>
+        <v>0.001714159302168647</v>
       </c>
       <c r="M43" t="n">
         <v>0.0118579054279053</v>
@@ -8145,7 +8145,7 @@
         <v>5.097596229596121e-05</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3337833952054449</v>
+        <v>0.3337833952054452</v>
       </c>
       <c r="I44" t="n">
         <v>0.2141925783101345</v>
@@ -8154,10 +8154,10 @@
         <v>0.01501563801209415</v>
       </c>
       <c r="K44" t="n">
-        <v>0.001939198019946954</v>
+        <v>0.001939198019946664</v>
       </c>
       <c r="L44" t="n">
-        <v>0.002759979207316603</v>
+        <v>0.002759979207316065</v>
       </c>
       <c r="M44" t="n">
         <v>0.0100756110556108</v>
@@ -8195,10 +8195,10 @@
         <v>0.01432544185288372</v>
       </c>
       <c r="K45" t="n">
-        <v>0.003078479668631209</v>
+        <v>0.003078479668631244</v>
       </c>
       <c r="L45" t="n">
-        <v>0.001947773454487273</v>
+        <v>0.001947773454487344</v>
       </c>
       <c r="M45" t="n">
         <v>0.0135180119880118</v>
@@ -8227,7 +8227,7 @@
         <v>0.0001442105306485665</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3415065658096758</v>
+        <v>0.3415065658096752</v>
       </c>
       <c r="I46" t="n">
         <v>0.2112871702496314</v>
@@ -8236,10 +8236,10 @@
         <v>0.01449037322291817</v>
       </c>
       <c r="K46" t="n">
-        <v>0.001614204517366581</v>
+        <v>0.001614204517367096</v>
       </c>
       <c r="L46" t="n">
-        <v>0.00131334989130995</v>
+        <v>0.001313349891311084</v>
       </c>
       <c r="M46" t="n">
         <v>0.0461269463869462</v>
@@ -8277,10 +8277,10 @@
         <v>0.01572221625402013</v>
       </c>
       <c r="K47" t="n">
-        <v>0.01562907906514331</v>
+        <v>0.01562907906514319</v>
       </c>
       <c r="L47" t="n">
-        <v>0.0009673031233989511</v>
+        <v>0.0009673031233987037</v>
       </c>
       <c r="M47" t="n">
         <v>0.1434368331668326</v>
@@ -8309,7 +8309,7 @@
         <v>4.445012008621641e-05</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3275871257067838</v>
+        <v>0.3275871257067841</v>
       </c>
       <c r="I48" t="n">
         <v>0.2242333015406099</v>
@@ -8318,10 +8318,10 @@
         <v>0.0152034971111829</v>
       </c>
       <c r="K48" t="n">
-        <v>0.005407023582668121</v>
+        <v>0.00540702358266785</v>
       </c>
       <c r="L48" t="n">
-        <v>0.002456380787740682</v>
+        <v>0.00245638078774021</v>
       </c>
       <c r="M48" t="n">
         <v>0.011637056277056</v>
@@ -8350,7 +8350,7 @@
         <v>0.0001988907963135489</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3726045543058478</v>
+        <v>0.3726045543058487</v>
       </c>
       <c r="I49" t="n">
         <v>0.06266210533397996</v>
@@ -8359,10 +8359,10 @@
         <v>0.0123439618579128</v>
       </c>
       <c r="K49" t="n">
-        <v>9.425559994798912e-06</v>
+        <v>9.425559993823858e-06</v>
       </c>
       <c r="L49" t="n">
-        <v>0.004366106382714475</v>
+        <v>0.004366106382712487</v>
       </c>
       <c r="M49" t="n">
         <v>0.0014716516816516</v>
@@ -8391,7 +8391,7 @@
         <v>0.0001308281985121224</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3032497656896036</v>
+        <v>0.3032497656896037</v>
       </c>
       <c r="I50" t="n">
         <v>0.2646037512933648</v>
@@ -8400,10 +8400,10 @@
         <v>0.0156618164690161</v>
       </c>
       <c r="K50" t="n">
-        <v>0.01529742281652155</v>
+        <v>0.01529742281652144</v>
       </c>
       <c r="L50" t="n">
-        <v>0.001032451201428524</v>
+        <v>0.001032451201428293</v>
       </c>
       <c r="M50" t="n">
         <v>0.1465683316683311</v>
@@ -8432,7 +8432,7 @@
         <v>0.0001407471507278494</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3037127392379255</v>
+        <v>0.3037127392379256</v>
       </c>
       <c r="I51" t="n">
         <v>0.2632587695232995</v>
@@ -8441,10 +8441,10 @@
         <v>0.01563020033650687</v>
       </c>
       <c r="K51" t="n">
-        <v>0.01519542526765466</v>
+        <v>0.01519542526765456</v>
       </c>
       <c r="L51" t="n">
-        <v>0.001048666905399457</v>
+        <v>0.001048666905399249</v>
       </c>
       <c r="M51" t="n">
         <v>0.1475534698634692</v>
@@ -8482,10 +8482,10 @@
         <v>0.01442237183571255</v>
       </c>
       <c r="K52" t="n">
-        <v>0.001642318297350802</v>
+        <v>0.001642318297350637</v>
       </c>
       <c r="L52" t="n">
-        <v>0.002213017854101321</v>
+        <v>0.002213017854101005</v>
       </c>
       <c r="M52" t="n">
         <v>0.0311853879453873</v>
@@ -8514,7 +8514,7 @@
         <v>4.489247622091228e-05</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3142772615247704</v>
+        <v>0.3142772615247703</v>
       </c>
       <c r="I53" t="n">
         <v>0.2337728198263059</v>
@@ -8523,10 +8523,10 @@
         <v>0.01539087295107979</v>
       </c>
       <c r="K53" t="n">
-        <v>0.02076171209582481</v>
+        <v>0.02076171209582493</v>
       </c>
       <c r="L53" t="n">
-        <v>0.00151238284857944</v>
+        <v>0.001512382848579676</v>
       </c>
       <c r="M53" t="n">
         <v>0.0028190775890774</v>
@@ -8555,7 +8555,7 @@
         <v>2.970846309151682e-05</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3305702812071837</v>
+        <v>0.3305702812071838</v>
       </c>
       <c r="I54" t="n">
         <v>0.2458708944143893</v>
@@ -8564,10 +8564,10 @@
         <v>0.01547151868856055</v>
       </c>
       <c r="K54" t="n">
-        <v>0.02049396440588156</v>
+        <v>0.02049396440588151</v>
       </c>
       <c r="L54" t="n">
-        <v>0.001205521741665718</v>
+        <v>0.001205521741665551</v>
       </c>
       <c r="M54" t="n">
         <v>0.004389703629703401</v>
@@ -8596,7 +8596,7 @@
         <v>0.0001487846362383405</v>
       </c>
       <c r="H55" t="n">
-        <v>0.304085972179491</v>
+        <v>0.3040859721794911</v>
       </c>
       <c r="I55" t="n">
         <v>0.2621746118915473</v>
@@ -8605,10 +8605,10 @@
         <v>0.01560467130694163</v>
       </c>
       <c r="K55" t="n">
-        <v>0.0151131991533249</v>
+        <v>0.01511319915332479</v>
       </c>
       <c r="L55" t="n">
-        <v>0.00106182200570567</v>
+        <v>0.001061822005705432</v>
       </c>
       <c r="M55" t="n">
         <v>0.1483573493173486</v>
@@ -8637,7 +8637,7 @@
         <v>0.0003822077604751447</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3414013284970748</v>
+        <v>0.341401328497075</v>
       </c>
       <c r="I56" t="n">
         <v>0.1689516981190775</v>
@@ -8646,10 +8646,10 @@
         <v>0.013839050269581</v>
       </c>
       <c r="K56" t="n">
-        <v>0.0003662538722618552</v>
+        <v>0.0003662538722618273</v>
       </c>
       <c r="L56" t="n">
-        <v>0.003224557099766759</v>
+        <v>0.003224557099766648</v>
       </c>
       <c r="M56" t="n">
         <v>0.0127463303363301</v>
@@ -8678,7 +8678,7 @@
         <v>0.0002035786487847892</v>
       </c>
       <c r="H57" t="n">
-        <v>0.3041952637186313</v>
+        <v>0.3041952637186264</v>
       </c>
       <c r="I57" t="n">
         <v>0.2609867707315987</v>
@@ -8687,10 +8687,10 @@
         <v>0.01554897177427505</v>
       </c>
       <c r="K57" t="n">
-        <v>0.01504436418480751</v>
+        <v>0.01504436418481239</v>
       </c>
       <c r="L57" t="n">
-        <v>0.001078627069160759</v>
+        <v>0.001078627069170508</v>
       </c>
       <c r="M57" t="n">
         <v>0.1490361538461531</v>
@@ -8719,7 +8719,7 @@
         <v>0.0002331186056150917</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3450014168890027</v>
+        <v>0.3450014168890012</v>
       </c>
       <c r="I58" t="n">
         <v>0.134691061747631</v>
@@ -8728,10 +8728,10 @@
         <v>0.01401975376174151</v>
       </c>
       <c r="K58" t="n">
-        <v>0.009264108960209225</v>
+        <v>0.009264108960210697</v>
       </c>
       <c r="L58" t="n">
-        <v>0.003429436649357192</v>
+        <v>0.003429436649360137</v>
       </c>
       <c r="M58" t="n">
         <v>0.0052441158841156</v>
@@ -8760,7 +8760,7 @@
         <v>0.0002015554595754072</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3036116878654392</v>
+        <v>0.3036116878654344</v>
       </c>
       <c r="I59" t="n">
         <v>0.2613810996082338</v>
@@ -8769,10 +8769,10 @@
         <v>0.0155626844779708</v>
       </c>
       <c r="K59" t="n">
-        <v>0.01524703121892556</v>
+        <v>0.01524703121893039</v>
       </c>
       <c r="L59" t="n">
-        <v>0.001073615802106107</v>
+        <v>0.001073615802115753</v>
       </c>
       <c r="M59" t="n">
         <v>0.1507356576756569</v>
@@ -8801,7 +8801,7 @@
         <v>0.0001306387986936479</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3449199221776192</v>
+        <v>0.3449199221776188</v>
       </c>
       <c r="I60" t="n">
         <v>0.2129236463331416</v>
@@ -8810,10 +8810,10 @@
         <v>0.0145611098407767</v>
       </c>
       <c r="K60" t="n">
-        <v>0.001485956106842228</v>
+        <v>0.001485956106842627</v>
       </c>
       <c r="L60" t="n">
-        <v>0.001369027208801808</v>
+        <v>0.00136902720880266</v>
       </c>
       <c r="M60" t="n">
         <v>0.059644958374958</v>
@@ -8842,7 +8842,7 @@
         <v>0.0001949777433988215</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3049419424765721</v>
+        <v>0.3049419424765674</v>
       </c>
       <c r="I61" t="n">
         <v>0.2617371328081278</v>
@@ -8851,10 +8851,10 @@
         <v>0.01557248777625395</v>
       </c>
       <c r="K61" t="n">
-        <v>0.01558636236168797</v>
+        <v>0.0155863623616926</v>
       </c>
       <c r="L61" t="n">
-        <v>0.001059117332150333</v>
+        <v>0.001059117332159584</v>
       </c>
       <c r="M61" t="n">
         <v>0.1568839427239419</v>
@@ -8883,7 +8883,7 @@
         <v>0.0003779755079014517</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3431688536868691</v>
+        <v>0.3431688536868689</v>
       </c>
       <c r="I62" t="n">
         <v>0.162893583243601</v>
@@ -8892,10 +8892,10 @@
         <v>0.01374821147214042</v>
       </c>
       <c r="K62" t="n">
-        <v>0.0003459820226810429</v>
+        <v>0.0003459820226812231</v>
       </c>
       <c r="L62" t="n">
-        <v>0.003245465950496227</v>
+        <v>0.003245465950496536</v>
       </c>
       <c r="M62" t="n">
         <v>0.0135116816516814</v>
@@ -8924,7 +8924,7 @@
         <v>0.0001984011194092675</v>
       </c>
       <c r="H63" t="n">
-        <v>0.3046163994221451</v>
+        <v>0.3046163994221405</v>
       </c>
       <c r="I63" t="n">
         <v>0.2611051406893775</v>
@@ -8933,10 +8933,10 @@
         <v>0.01557626036249269</v>
       </c>
       <c r="K63" t="n">
-        <v>0.01550296481511275</v>
+        <v>0.01550296481511734</v>
       </c>
       <c r="L63" t="n">
-        <v>0.001113707925021769</v>
+        <v>0.001113707925030936</v>
       </c>
       <c r="M63" t="n">
         <v>0.1582835298035289</v>
@@ -8965,7 +8965,7 @@
         <v>0.0001101488314117755</v>
       </c>
       <c r="H64" t="n">
-        <v>0.347230600879232</v>
+        <v>0.3472306008792314</v>
       </c>
       <c r="I64" t="n">
         <v>0.1912450403684092</v>
@@ -8974,10 +8974,10 @@
         <v>0.01420664613233082</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0003009892490035828</v>
+        <v>0.0003009892490041314</v>
       </c>
       <c r="L64" t="n">
-        <v>0.002247658939811702</v>
+        <v>0.002247658939812804</v>
       </c>
       <c r="M64" t="n">
         <v>0.0229950049950048</v>
@@ -9006,7 +9006,7 @@
         <v>0.000121636093429167</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3481314289291891</v>
+        <v>0.3481314289291885</v>
       </c>
       <c r="I65" t="n">
         <v>0.1866438675751318</v>
@@ -9015,10 +9015,10 @@
         <v>0.01413218500356929</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0002905706900919967</v>
+        <v>0.0002905706900926348</v>
       </c>
       <c r="L65" t="n">
-        <v>0.002277831836171979</v>
+        <v>0.002277831836173254</v>
       </c>
       <c r="M65" t="n">
         <v>0.0238413586413584</v>
@@ -9047,7 +9047,7 @@
         <v>0.0001391386019244572</v>
       </c>
       <c r="H66" t="n">
-        <v>0.3452147743313611</v>
+        <v>0.3452147743313607</v>
       </c>
       <c r="I66" t="n">
         <v>0.2113120131225769</v>
@@ -9056,10 +9056,10 @@
         <v>0.01452972507390196</v>
       </c>
       <c r="K66" t="n">
-        <v>0.001470210739089391</v>
+        <v>0.001470210739089767</v>
       </c>
       <c r="L66" t="n">
-        <v>0.001381728124626216</v>
+        <v>0.001381728124627021</v>
       </c>
       <c r="M66" t="n">
         <v>0.0602869930069926</v>
@@ -9088,7 +9088,7 @@
         <v>0.0002097714751917632</v>
       </c>
       <c r="H67" t="n">
-        <v>0.3726047024581183</v>
+        <v>0.372604702458118</v>
       </c>
       <c r="I67" t="n">
         <v>0.06255270048917036</v>
@@ -9097,10 +9097,10 @@
         <v>0.01233308117903457</v>
       </c>
       <c r="K67" t="n">
-        <v>9.277407724270222e-06</v>
+        <v>9.277407724604964e-06</v>
       </c>
       <c r="L67" t="n">
-        <v>0.004245524554485649</v>
+        <v>0.004245524554486311</v>
       </c>
       <c r="M67" t="n">
         <v>0.002195591075591</v>
@@ -9129,7 +9129,7 @@
         <v>0.0001986041620129554</v>
       </c>
       <c r="H68" t="n">
-        <v>0.3045568360950889</v>
+        <v>0.3045568360950843</v>
       </c>
       <c r="I68" t="n">
         <v>0.2606604665756481</v>
@@ -9138,10 +9138,10 @@
         <v>0.01556639775382514</v>
       </c>
       <c r="K68" t="n">
-        <v>0.01532540845898105</v>
+        <v>0.01532540845898558</v>
       </c>
       <c r="L68" t="n">
-        <v>0.001138471433896497</v>
+        <v>0.001138471433905557</v>
       </c>
       <c r="M68" t="n">
         <v>0.1601949317349308</v>
@@ -9179,10 +9179,10 @@
         <v>0.01441116925433658</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0012266589385295</v>
+        <v>0.001226658938529547</v>
       </c>
       <c r="L69" t="n">
-        <v>0.00161079468341703</v>
+        <v>0.00161079468341714</v>
       </c>
       <c r="M69" t="n">
         <v>0.073798674658674</v>
@@ -9211,7 +9211,7 @@
         <v>0.0001974909998339879</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3049308996051296</v>
+        <v>0.304930899605125</v>
       </c>
       <c r="I70" t="n">
         <v>0.2606830428602073</v>
@@ -9220,10 +9220,10 @@
         <v>0.01556648464914186</v>
       </c>
       <c r="K70" t="n">
-        <v>0.01537191029842102</v>
+        <v>0.01537191029842552</v>
       </c>
       <c r="L70" t="n">
-        <v>0.001136030461635366</v>
+        <v>0.001136030461644357</v>
       </c>
       <c r="M70" t="n">
         <v>0.1613267698967689</v>
@@ -9261,10 +9261,10 @@
         <v>0.01436756263137864</v>
       </c>
       <c r="K71" t="n">
-        <v>0.001208416621396547</v>
+        <v>0.001208416621396618</v>
       </c>
       <c r="L71" t="n">
-        <v>0.001627175861377043</v>
+        <v>0.001627175861377203</v>
       </c>
       <c r="M71" t="n">
         <v>0.0749212287712281</v>
@@ -9293,7 +9293,7 @@
         <v>0.0001598828788073737</v>
       </c>
       <c r="H72" t="n">
-        <v>0.3094958789437613</v>
+        <v>0.3094958789437565</v>
       </c>
       <c r="I72" t="n">
         <v>0.2508015652901827</v>
@@ -9302,10 +9302,10 @@
         <v>0.01540292627783888</v>
       </c>
       <c r="K72" t="n">
-        <v>0.01310926957897055</v>
+        <v>0.01310926957897522</v>
       </c>
       <c r="L72" t="n">
-        <v>0.001280454918927256</v>
+        <v>0.001280454918936593</v>
       </c>
       <c r="M72" t="n">
         <v>0.1925121578421562</v>
@@ -9334,7 +9334,7 @@
         <v>0.0001587728778111515</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3106083359285352</v>
+        <v>0.3106083359285304</v>
       </c>
       <c r="I73" t="n">
         <v>0.2480339195289949</v>
@@ -9343,10 +9343,10 @@
         <v>0.01536929927558124</v>
       </c>
       <c r="K73" t="n">
-        <v>0.01283638488440225</v>
+        <v>0.01283638488440684</v>
       </c>
       <c r="L73" t="n">
-        <v>0.001310038373730146</v>
+        <v>0.001310038373739316</v>
       </c>
       <c r="M73" t="n">
         <v>0.1977562737262718</v>
@@ -9375,7 +9375,7 @@
         <v>0.0002347973588831568</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3726050644904491</v>
+        <v>0.3726050644904498</v>
       </c>
       <c r="I74" t="n">
         <v>0.06230419731251505</v>
@@ -9384,10 +9384,10 @@
         <v>0.01230805529534324</v>
       </c>
       <c r="K74" t="n">
-        <v>8.915375393452687e-06</v>
+        <v>8.915375392767332e-06</v>
       </c>
       <c r="L74" t="n">
-        <v>0.003971271429477266</v>
+        <v>0.003971271429475893</v>
       </c>
       <c r="M74" t="n">
         <v>0.0057774891774891</v>
@@ -9416,7 +9416,7 @@
         <v>0.0001715270464715075</v>
       </c>
       <c r="H75" t="n">
-        <v>0.3123681385962523</v>
+        <v>0.3123681385962475</v>
       </c>
       <c r="I75" t="n">
         <v>0.2427201634304198</v>
@@ -9425,10 +9425,10 @@
         <v>0.01527180696272897</v>
       </c>
       <c r="K75" t="n">
-        <v>0.01247229592035022</v>
+        <v>0.01247229592035492</v>
       </c>
       <c r="L75" t="n">
-        <v>0.001333393696651716</v>
+        <v>0.001333393696661113</v>
       </c>
       <c r="M75" t="n">
         <v>0.2035337629037609</v>
@@ -9457,7 +9457,7 @@
         <v>0.0001177692042454552</v>
       </c>
       <c r="H76" t="n">
-        <v>0.3497948985677198</v>
+        <v>0.3497948985677192</v>
       </c>
       <c r="I76" t="n">
         <v>0.1868256886289912</v>
@@ -9466,10 +9466,10 @@
         <v>0.01413358323537187</v>
       </c>
       <c r="K76" t="n">
-        <v>0.0004946802223430746</v>
+        <v>0.0004946802223437321</v>
       </c>
       <c r="L76" t="n">
-        <v>0.002293773566510067</v>
+        <v>0.002293773566511381</v>
       </c>
       <c r="M76" t="n">
         <v>0.0255375824175821</v>
@@ -9498,7 +9498,7 @@
         <v>0.0001678933923102256</v>
       </c>
       <c r="H77" t="n">
-        <v>0.3126279967740146</v>
+        <v>0.3126279967740097</v>
       </c>
       <c r="I77" t="n">
         <v>0.2429399054164499</v>
@@ -9507,10 +9507,10 @@
         <v>0.01527618945955487</v>
       </c>
       <c r="K77" t="n">
-        <v>0.01244721185574597</v>
+        <v>0.01244721185575065</v>
       </c>
       <c r="L77" t="n">
-        <v>0.001332421476315716</v>
+        <v>0.001332421476325073</v>
       </c>
       <c r="M77" t="n">
         <v>0.2044065001664981</v>
@@ -9548,10 +9548,10 @@
         <v>0.01438293213825033</v>
       </c>
       <c r="K78" t="n">
-        <v>0.001440383085577736</v>
+        <v>0.0014403830855778</v>
       </c>
       <c r="L78" t="n">
-        <v>0.001612409654152752</v>
+        <v>0.001612409654152898</v>
       </c>
       <c r="M78" t="n">
         <v>0.0758633133533126</v>
@@ -9580,7 +9580,7 @@
         <v>0.0001688540947501943</v>
       </c>
       <c r="H79" t="n">
-        <v>0.3128203171895807</v>
+        <v>0.3128203171895755</v>
       </c>
       <c r="I79" t="n">
         <v>0.2423539418677699</v>
@@ -9589,10 +9589,10 @@
         <v>0.01526592265699274</v>
       </c>
       <c r="K79" t="n">
-        <v>0.01240737867306752</v>
+        <v>0.0124073786730724</v>
       </c>
       <c r="L79" t="n">
-        <v>0.001333719284723208</v>
+        <v>0.001333719284732969</v>
       </c>
       <c r="M79" t="n">
         <v>0.2050642723942703</v>
@@ -9621,7 +9621,7 @@
         <v>0.0001707938567319179</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3131393921581433</v>
+        <v>0.3131393921581384</v>
       </c>
       <c r="I80" t="n">
         <v>0.2413826688090585</v>
@@ -9630,10 +9630,10 @@
         <v>0.01524854508081847</v>
       </c>
       <c r="K80" t="n">
-        <v>0.01234126354129477</v>
+        <v>0.01234126354129944</v>
       </c>
       <c r="L80" t="n">
-        <v>0.001336230904319453</v>
+        <v>0.001336230904328783</v>
       </c>
       <c r="M80" t="n">
         <v>0.2061648318348297</v>
@@ -9671,10 +9671,10 @@
         <v>0.0150287065299689</v>
       </c>
       <c r="K81" t="n">
-        <v>0.005413871329782049</v>
+        <v>0.005413871329781919</v>
       </c>
       <c r="L81" t="n">
-        <v>0.002856182717016837</v>
+        <v>0.002856182717016668</v>
       </c>
       <c r="M81" t="n">
         <v>0.0190199800199795</v>
@@ -9703,7 +9703,7 @@
         <v>0.0001722366825666499</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3133915402353631</v>
+        <v>0.313391540235358</v>
       </c>
       <c r="I82" t="n">
         <v>0.2406148681620243</v>
@@ -9712,10 +9712,10 @@
         <v>0.01523490206791773</v>
       </c>
       <c r="K82" t="n">
-        <v>0.01228902442077907</v>
+        <v>0.01228902442078389</v>
       </c>
       <c r="L82" t="n">
-        <v>0.001338103006931113</v>
+        <v>0.001338103006940752</v>
       </c>
       <c r="M82" t="n">
         <v>0.2070429736929715</v>
@@ -9744,7 +9744,7 @@
         <v>8.212116167008569e-05</v>
       </c>
       <c r="H83" t="n">
-        <v>0.3231730595855541</v>
+        <v>0.3231730595855544</v>
       </c>
       <c r="I83" t="n">
         <v>0.1984248921147667</v>
@@ -9753,10 +9753,10 @@
         <v>0.01470275041941204</v>
       </c>
       <c r="K83" t="n">
-        <v>0.004799464862412115</v>
+        <v>0.004799464862411846</v>
       </c>
       <c r="L83" t="n">
-        <v>0.002897494407473246</v>
+        <v>0.002897494407472788</v>
       </c>
       <c r="M83" t="n">
         <v>0.021458774558774</v>
@@ -9785,7 +9785,7 @@
         <v>0.0001881994463570869</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3460422682349611</v>
+        <v>0.346042268234961</v>
       </c>
       <c r="I84" t="n">
         <v>0.1982059976154738</v>
@@ -9794,10 +9794,10 @@
         <v>0.01432234173944091</v>
       </c>
       <c r="K84" t="n">
-        <v>0.001410473002360007</v>
+        <v>0.001410473002360134</v>
       </c>
       <c r="L84" t="n">
-        <v>0.001635371532310227</v>
+        <v>0.001635371532310498</v>
       </c>
       <c r="M84" t="n">
         <v>0.0774828171828164</v>
@@ -9826,7 +9826,7 @@
         <v>0.0001857874896651006</v>
       </c>
       <c r="H85" t="n">
-        <v>0.3138093126982767</v>
+        <v>0.3138093126982716</v>
       </c>
       <c r="I85" t="n">
         <v>0.2393696717111454</v>
@@ -9835,10 +9835,10 @@
         <v>0.01520113574143921</v>
       </c>
       <c r="K85" t="n">
-        <v>0.01220249797619604</v>
+        <v>0.01220249797620082</v>
       </c>
       <c r="L85" t="n">
-        <v>0.001357148135437836</v>
+        <v>0.001357148135447402</v>
       </c>
       <c r="M85" t="n">
         <v>0.2085146253746231</v>
@@ -9867,7 +9867,7 @@
         <v>0.000199122191472032</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3142175087345598</v>
+        <v>0.3142175087345548</v>
       </c>
       <c r="I86" t="n">
         <v>0.2381527967363804</v>
@@ -9876,10 +9876,10 @@
         <v>0.01516804887938824</v>
       </c>
       <c r="K86" t="n">
-        <v>0.01211795548109825</v>
+        <v>0.01211795548110298</v>
       </c>
       <c r="L86" t="n">
-        <v>0.001375443976000638</v>
+        <v>0.001375443976010106</v>
       </c>
       <c r="M86" t="n">
         <v>0.2099728937728914</v>
@@ -9917,10 +9917,10 @@
         <v>0.01438786841760344</v>
       </c>
       <c r="K87" t="n">
-        <v>0.001445125096044368</v>
+        <v>0.001445125096044449</v>
       </c>
       <c r="L87" t="n">
-        <v>0.001820879233131501</v>
+        <v>0.001820879233131701</v>
       </c>
       <c r="M87" t="n">
         <v>0.0989415917415904</v>
@@ -9949,7 +9949,7 @@
         <v>0.00021840396110095</v>
       </c>
       <c r="H88" t="n">
-        <v>0.3149450522065121</v>
+        <v>0.3149450522065073</v>
       </c>
       <c r="I88" t="n">
         <v>0.23527598769583</v>
@@ -9958,10 +9958,10 @@
         <v>0.01509921445092405</v>
       </c>
       <c r="K88" t="n">
-        <v>0.01177211222592525</v>
+        <v>0.0117721122259298</v>
       </c>
       <c r="L88" t="n">
-        <v>0.001479374357260281</v>
+        <v>0.001479374357269387</v>
       </c>
       <c r="M88" t="n">
         <v>0.2162077355977331</v>
@@ -9990,7 +9990,7 @@
         <v>0.0002246098341677578</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3151286636822024</v>
+        <v>0.3151286636821976</v>
       </c>
       <c r="I89" t="n">
         <v>0.2347313316175139</v>
@@ -9999,10 +9999,10 @@
         <v>0.01508416937000535</v>
       </c>
       <c r="K89" t="n">
-        <v>0.0117347082238625</v>
+        <v>0.01173470822386704</v>
       </c>
       <c r="L89" t="n">
-        <v>0.001487653263025987</v>
+        <v>0.001487653263035063</v>
       </c>
       <c r="M89" t="n">
         <v>0.2168986813186788</v>
@@ -10031,7 +10031,7 @@
         <v>0.0002010227647069203</v>
       </c>
       <c r="H90" t="n">
-        <v>0.3187829939085501</v>
+        <v>0.3187829939085468</v>
       </c>
       <c r="I90" t="n">
         <v>0.229666733930582</v>
@@ -10040,10 +10040,10 @@
         <v>0.01499636995489399</v>
       </c>
       <c r="K90" t="n">
-        <v>0.01054803147398588</v>
+        <v>0.01054803147398893</v>
       </c>
       <c r="L90" t="n">
-        <v>0.001561189154389111</v>
+        <v>0.001561189154395211</v>
       </c>
       <c r="M90" t="n">
         <v>0.2424362637362609</v>
@@ -10072,7 +10072,7 @@
         <v>0.0002116329665945911</v>
       </c>
       <c r="H91" t="n">
-        <v>0.3726047532806658</v>
+        <v>0.3726047532806649</v>
       </c>
       <c r="I91" t="n">
         <v>0.0625171218568646</v>
@@ -10081,10 +10081,10 @@
         <v>0.01233121968763176</v>
       </c>
       <c r="K91" t="n">
-        <v>9.226585176829844e-06</v>
+        <v>9.226585177640093e-06</v>
       </c>
       <c r="L91" t="n">
-        <v>0.004207982785682048</v>
+        <v>0.004207982785683728</v>
       </c>
       <c r="M91" t="n">
         <v>0.0038506027306026</v>
@@ -10113,7 +10113,7 @@
         <v>0.0002041223167814259</v>
       </c>
       <c r="H92" t="n">
-        <v>0.3192660042954709</v>
+        <v>0.3192660042954677</v>
       </c>
       <c r="I92" t="n">
         <v>0.228149982698479</v>
@@ -10122,10 +10122,10 @@
         <v>0.01496944568677088</v>
       </c>
       <c r="K92" t="n">
-        <v>0.01045348917378198</v>
+        <v>0.01045348917378492</v>
       </c>
       <c r="L92" t="n">
-        <v>0.001565459030593606</v>
+        <v>0.001565459030599482</v>
       </c>
       <c r="M92" t="n">
         <v>0.2446318548118519</v>
@@ -10154,7 +10154,7 @@
         <v>0.0001978919860003714</v>
       </c>
       <c r="H93" t="n">
-        <v>0.3197058972784799</v>
+        <v>0.3197058972784767</v>
       </c>
       <c r="I93" t="n">
         <v>0.228939654708188</v>
@@ -10163,10 +10163,10 @@
         <v>0.01498145192932729</v>
       </c>
       <c r="K93" t="n">
-        <v>0.01038985733276888</v>
+        <v>0.0103898573327718</v>
       </c>
       <c r="L93" t="n">
-        <v>0.001558314372042568</v>
+        <v>0.001558314372048402</v>
       </c>
       <c r="M93" t="n">
         <v>0.2490215584415553</v>
@@ -10195,7 +10195,7 @@
         <v>0.000231910266934976</v>
       </c>
       <c r="H94" t="n">
-        <v>0.3205110358316896</v>
+        <v>0.3205110358316865</v>
       </c>
       <c r="I94" t="n">
         <v>0.2264402008002946</v>
@@ -10204,10 +10204,10 @@
         <v>0.01490728656220436</v>
       </c>
       <c r="K94" t="n">
-        <v>0.01023216369206672</v>
+        <v>0.0102321636920696</v>
       </c>
       <c r="L94" t="n">
-        <v>0.001600347112849977</v>
+        <v>0.00160034711285573</v>
       </c>
       <c r="M94" t="n">
         <v>0.2528721611721579</v>
@@ -10236,7 +10236,7 @@
         <v>0.0008826121182107592</v>
       </c>
       <c r="H95" t="n">
-        <v>0.3247694859549724</v>
+        <v>0.3247694859549687</v>
       </c>
       <c r="I95" t="n">
         <v>0.2172410546915407</v>
@@ -10245,10 +10245,10 @@
         <v>0.01409651877991788</v>
       </c>
       <c r="K95" t="n">
-        <v>0.009484795963213853</v>
+        <v>0.009484795963217437</v>
       </c>
       <c r="L95" t="n">
-        <v>0.002799345709929259</v>
+        <v>0.002799345709936353</v>
       </c>
       <c r="M95" t="n">
         <v>0.3518137529137483</v>
@@ -10271,25 +10271,25 @@
         <v>0.02115818958026103</v>
       </c>
       <c r="F96" t="n">
-        <v>0.05505101129491923</v>
+        <v>0.05505101129297436</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0009099760448885302</v>
+        <v>0.0009099760443728607</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3247774933122629</v>
+        <v>0.3247774933130794</v>
       </c>
       <c r="I96" t="n">
-        <v>0.2167191558524931</v>
+        <v>0.216719155854438</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0140705461857597</v>
+        <v>0.01407054618627537</v>
       </c>
       <c r="K96" t="n">
-        <v>0.009461866009525866</v>
+        <v>0.009461866008709277</v>
       </c>
       <c r="L96" t="n">
-        <v>0.002803978459316943</v>
+        <v>0.002803978460144233</v>
       </c>
       <c r="M96" t="n">
         <v>0.352666343656339</v>
@@ -10312,25 +10312,25 @@
         <v>0.02115435940146725</v>
       </c>
       <c r="F97" t="n">
-        <v>0.05560534954405962</v>
+        <v>0.05560534954211945</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0009373226567731517</v>
+        <v>0.000937322656258731</v>
       </c>
       <c r="H97" t="n">
-        <v>0.3247854958859074</v>
+        <v>0.3247854958867165</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2161975811213743</v>
+        <v>0.2161975811233144</v>
       </c>
       <c r="J97" t="n">
-        <v>0.01404459007039679</v>
+        <v>0.01404459007091121</v>
       </c>
       <c r="K97" t="n">
-        <v>0.009438949805894778</v>
+        <v>0.009438949805085509</v>
       </c>
       <c r="L97" t="n">
-        <v>0.002808619761708995</v>
+        <v>0.002808619762544962</v>
       </c>
       <c r="M97" t="n">
         <v>0.3535225607725561</v>
@@ -10440,7 +10440,7 @@
         <v>7.991559184829622e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3093103552160814</v>
+        <v>0.3093103552160815</v>
       </c>
       <c r="I2" t="n">
         <v>0.2742343513785103</v>
@@ -10449,10 +10449,10 @@
         <v>0.01584648786138455</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006688868689835301</v>
+        <v>0.006688868689835266</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007496943707061538</v>
+        <v>0.0007496943707060855</v>
       </c>
       <c r="M2" t="n">
         <v>0.0190536996336995</v>
@@ -10481,7 +10481,7 @@
         <v>0.0003434731711125604</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3488333179495487</v>
+        <v>0.3488333179495182</v>
       </c>
       <c r="I3" t="n">
         <v>0.1780414431463274</v>
@@ -10490,10 +10490,10 @@
         <v>0.01386352671229844</v>
       </c>
       <c r="K3" t="n">
-        <v>7.372797275750884e-05</v>
+        <v>7.372797278797879e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002316082333516491</v>
+        <v>0.002316082333577421</v>
       </c>
       <c r="M3" t="n">
         <v>0.0314024408924408</v>
@@ -10531,10 +10531,10 @@
         <v>0.01595828297439843</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009406066205174863</v>
+        <v>0.00940606620517483</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007119047489492577</v>
+        <v>0.0007119047489491691</v>
       </c>
       <c r="M4" t="n">
         <v>0.0212730536130534</v>
@@ -10563,7 +10563,7 @@
         <v>0.0002076617898202348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3726046941310902</v>
+        <v>0.3726046941310896</v>
       </c>
       <c r="I5" t="n">
         <v>0.06255952651154183</v>
@@ -10572,10 +10572,10 @@
         <v>0.01233519086440617</v>
       </c>
       <c r="K5" t="n">
-        <v>9.285734752439523e-06</v>
+        <v>9.285734752966143e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004254476916284913</v>
+        <v>0.004254476916285963</v>
       </c>
       <c r="M5" t="n">
         <v>0.0032074325674325</v>
@@ -10604,7 +10604,7 @@
         <v>0.000314982789409334</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3493444282068111</v>
+        <v>0.3493444282067838</v>
       </c>
       <c r="I6" t="n">
         <v>0.1798903303945101</v>
@@ -10613,10 +10613,10 @@
         <v>0.01390483441966107</v>
       </c>
       <c r="K6" t="n">
-        <v>8.087475397418007e-05</v>
+        <v>8.087475400136583e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002347836290461317</v>
+        <v>0.00234783629051568</v>
       </c>
       <c r="M6" t="n">
         <v>0.0351960139860138</v>
@@ -10645,7 +10645,7 @@
         <v>2.043650024772436e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3045714068232898</v>
+        <v>0.30457140682329</v>
       </c>
       <c r="I7" t="n">
         <v>0.2702153446937324</v>
@@ -10654,10 +10654,10 @@
         <v>0.01583481302281284</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009102784287493728</v>
+        <v>0.009102784287493566</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007913627048952249</v>
+        <v>0.0007913627048948787</v>
       </c>
       <c r="M7" t="n">
         <v>0.021982414252414</v>
@@ -10686,7 +10686,7 @@
         <v>3.34053976967516e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3067788416273317</v>
+        <v>0.3067788416273319</v>
       </c>
       <c r="I8" t="n">
         <v>0.263448777128118</v>
@@ -10695,10 +10695,10 @@
         <v>0.01571437147416178</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008807685356726384</v>
+        <v>0.008807685356726191</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0008676678358692971</v>
+        <v>0.0008676678358688905</v>
       </c>
       <c r="M8" t="n">
         <v>0.0227195637695635</v>
@@ -10727,7 +10727,7 @@
         <v>4.367092017522025e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3084828614086851</v>
+        <v>0.3084828614086854</v>
       </c>
       <c r="I9" t="n">
         <v>0.2582249341062692</v>
@@ -10736,10 +10736,10 @@
         <v>0.01562114296812123</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008579883830391188</v>
+        <v>0.008579883830390989</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009258897088847657</v>
+        <v>0.0009258897088843474</v>
       </c>
       <c r="M9" t="n">
         <v>0.023323313353313</v>
@@ -10768,7 +10768,7 @@
         <v>0.0003233453856266043</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3499877064578623</v>
+        <v>0.3499877064578358</v>
       </c>
       <c r="I10" t="n">
         <v>0.1766135141653508</v>
@@ -10777,10 +10777,10 @@
         <v>0.01385009958060063</v>
       </c>
       <c r="K10" t="n">
-        <v>7.882112126495187e-05</v>
+        <v>7.882112129135673e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002356753783097128</v>
+        <v>0.00235675378314993</v>
       </c>
       <c r="M10" t="n">
         <v>0.0361969497169495</v>
@@ -10850,7 +10850,7 @@
         <v>0.0002037200087041417</v>
       </c>
       <c r="H12" t="n">
-        <v>0.335532806922858</v>
+        <v>0.3355328069228421</v>
       </c>
       <c r="I12" t="n">
         <v>0.2121365860797532</v>
@@ -10859,10 +10859,10 @@
         <v>0.01455412534321614</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001601023157051814</v>
+        <v>0.001601023157067761</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00173136012401653</v>
+        <v>0.001731360124048475</v>
       </c>
       <c r="M12" t="n">
         <v>0.05952026307026249</v>
@@ -10891,7 +10891,7 @@
         <v>5.293610188459853e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3146341959625197</v>
+        <v>0.3146341959625198</v>
       </c>
       <c r="I13" t="n">
         <v>0.208376971129913</v>
@@ -10900,10 +10900,10 @@
         <v>0.01486093608248478</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01137460123720265</v>
+        <v>0.01137460123720263</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002796177262906202</v>
+        <v>0.00279617726290611</v>
       </c>
       <c r="M13" t="n">
         <v>0.0039805627705627</v>
@@ -10932,7 +10932,7 @@
         <v>0.0002216165920844272</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3726048717640411</v>
+        <v>0.3726048717640421</v>
       </c>
       <c r="I14" t="n">
         <v>0.06243331671746135</v>
@@ -10941,10 +10941,10 @@
         <v>0.01232123606214195</v>
       </c>
       <c r="K14" t="n">
-        <v>9.108101801468871e-06</v>
+        <v>9.108101800512786e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>0.004113957054038284</v>
+        <v>0.004113957054036377</v>
       </c>
       <c r="M14" t="n">
         <v>0.0031687845487844</v>
@@ -10973,7 +10973,7 @@
         <v>0.0002013508273728924</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3358372135485715</v>
+        <v>0.3358372135485558</v>
       </c>
       <c r="I15" t="n">
         <v>0.2128264116242172</v>
@@ -10982,10 +10982,10 @@
         <v>0.01456702677803448</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0018189460471389</v>
+        <v>0.001818946047154649</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001714861769169413</v>
+        <v>0.001714861769200964</v>
       </c>
       <c r="M15" t="n">
         <v>0.06025747252747189</v>
@@ -11014,7 +11014,7 @@
         <v>0.0002383581846133698</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3376954822181488</v>
+        <v>0.3376954822181339</v>
       </c>
       <c r="I16" t="n">
         <v>0.2051836832920696</v>
@@ -11023,10 +11023,10 @@
         <v>0.01441754432613535</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001727399490408125</v>
+        <v>0.001727399490423021</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001757906512158905</v>
+        <v>0.001757906512188747</v>
       </c>
       <c r="M16" t="n">
         <v>0.06346490509490439</v>
@@ -11055,7 +11055,7 @@
         <v>0.0002168523674487278</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3726048182190606</v>
+        <v>0.3726048182190611</v>
       </c>
       <c r="I17" t="n">
         <v>0.06247043138204018</v>
@@ -11064,10 +11064,10 @@
         <v>0.01232600028677766</v>
       </c>
       <c r="K17" t="n">
-        <v>9.161646782037676e-06</v>
+        <v>9.161646781452503e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004155943033213981</v>
+        <v>0.004155943033212813</v>
       </c>
       <c r="M17" t="n">
         <v>0.0051773293373291</v>
@@ -11096,7 +11096,7 @@
         <v>0.000218510008433679</v>
       </c>
       <c r="H18" t="n">
-        <v>0.372604828524281</v>
+        <v>0.3726048285242815</v>
       </c>
       <c r="I18" t="n">
         <v>0.06246322865194868</v>
@@ -11105,10 +11105,10 @@
         <v>0.0123243426457927</v>
       </c>
       <c r="K18" t="n">
-        <v>9.15134156159897e-06</v>
+        <v>9.151341561127207e-06</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004147062051696652</v>
+        <v>0.004147062051695711</v>
       </c>
       <c r="M18" t="n">
         <v>0.0060269663669661</v>
@@ -11137,7 +11137,7 @@
         <v>0.000232052495134829</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3391265580908049</v>
+        <v>0.3391265580907906</v>
       </c>
       <c r="I19" t="n">
         <v>0.2059935281223119</v>
@@ -11146,10 +11146,10 @@
         <v>0.01442300206278052</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00169003487103484</v>
+        <v>0.001690034871049226</v>
       </c>
       <c r="L19" t="n">
-        <v>0.001747621208363996</v>
+        <v>0.001747621208392816</v>
       </c>
       <c r="M19" t="n">
         <v>0.06587512487512409</v>
@@ -11178,7 +11178,7 @@
         <v>0.000376175857342074</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3389934411841711</v>
+        <v>0.338993441184157</v>
       </c>
       <c r="I20" t="n">
         <v>0.2035272160645536</v>
@@ -11187,10 +11187,10 @@
         <v>0.01428972086142087</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001669666116871014</v>
+        <v>0.001669666116885237</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001783504433073369</v>
+        <v>0.001783504433101864</v>
       </c>
       <c r="M20" t="n">
         <v>0.06667876123876039</v>
@@ -11219,7 +11219,7 @@
         <v>0.000380388285611285</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3392260312403708</v>
+        <v>0.3392260312403567</v>
       </c>
       <c r="I21" t="n">
         <v>0.2025460128419584</v>
@@ -11228,10 +11228,10 @@
         <v>0.01427081739428784</v>
       </c>
       <c r="K21" t="n">
-        <v>0.001658169686763989</v>
+        <v>0.001658169686778133</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0017894755918533</v>
+        <v>0.001789475591881638</v>
       </c>
       <c r="M21" t="n">
         <v>0.06714337995337909</v>
@@ -11260,7 +11260,7 @@
         <v>0.0003646433886635448</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3382837460379476</v>
+        <v>0.3382837460379343</v>
       </c>
       <c r="I22" t="n">
         <v>0.2037018181012682</v>
@@ -11269,10 +11269,10 @@
         <v>0.01430126283325736</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001767929638101775</v>
+        <v>0.00176792963811517</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001804631607027739</v>
+        <v>0.001804631607054569</v>
       </c>
       <c r="M22" t="n">
         <v>0.07112394272394179</v>
@@ -11301,7 +11301,7 @@
         <v>0.0002207468970332183</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3726048464456315</v>
+        <v>0.372604846445632</v>
       </c>
       <c r="I23" t="n">
         <v>0.06245113817495155</v>
@@ -11310,10 +11310,10 @@
         <v>0.01232210575719316</v>
       </c>
       <c r="K23" t="n">
-        <v>9.133420211109206e-06</v>
+        <v>9.133420210640844e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004132698843398997</v>
+        <v>0.004132698843398063</v>
       </c>
       <c r="M23" t="n">
         <v>0.006858381618381299</v>
@@ -11342,7 +11342,7 @@
         <v>0.0004223792286493911</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3413022471353771</v>
+        <v>0.3413022471353651</v>
       </c>
       <c r="I24" t="n">
         <v>0.1912193509987543</v>
@@ -11351,10 +11351,10 @@
         <v>0.01405680889162072</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0016132147946839</v>
+        <v>0.001613214794695955</v>
       </c>
       <c r="L24" t="n">
-        <v>0.001879157664677972</v>
+        <v>0.001879157664702118</v>
       </c>
       <c r="M24" t="n">
         <v>0.07798232434232309</v>
@@ -11383,7 +11383,7 @@
         <v>0.0004199943986351719</v>
       </c>
       <c r="H25" t="n">
-        <v>0.342066759516002</v>
+        <v>0.3420667595159902</v>
       </c>
       <c r="I25" t="n">
         <v>0.1902044447830702</v>
@@ -11392,10 +11392,10 @@
         <v>0.01403910282467112</v>
       </c>
       <c r="K25" t="n">
-        <v>0.001578142177388576</v>
+        <v>0.001578142177400392</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001908784402901108</v>
+        <v>0.001908784402924774</v>
       </c>
       <c r="M25" t="n">
         <v>0.07979201132201</v>
@@ -11424,7 +11424,7 @@
         <v>0.000211165162876576</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3726047195712007</v>
+        <v>0.3726047195712027</v>
       </c>
       <c r="I26" t="n">
         <v>0.06254021240425273</v>
@@ -11433,10 +11433,10 @@
         <v>0.01233168749134982</v>
       </c>
       <c r="K26" t="n">
-        <v>9.260294641837271e-06</v>
+        <v>9.26029463985776e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>0.00423160855571824</v>
+        <v>0.004231608555714278</v>
       </c>
       <c r="M26" t="n">
         <v>0.0021071961371961</v>
@@ -11465,7 +11465,7 @@
         <v>0.0004372238784517172</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3428524577528168</v>
+        <v>0.3428524577528054</v>
       </c>
       <c r="I27" t="n">
         <v>0.18690489833259</v>
@@ -11474,10 +11474,10 @@
         <v>0.01397257002093781</v>
       </c>
       <c r="K27" t="n">
-        <v>0.001537793395310938</v>
+        <v>0.001537793395322334</v>
       </c>
       <c r="L27" t="n">
-        <v>0.001931124989990908</v>
+        <v>0.001931124990013731</v>
       </c>
       <c r="M27" t="n">
         <v>0.08189920745920609</v>
